--- a/research/traditional_assets/database/data/kenya/kenya_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_construction_supplies.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.148416504725415</v>
+        <v>0.1480027552112387</v>
       </c>
       <c r="C2">
-        <v>154.1</v>
+        <v>152.7942074239482</v>
       </c>
       <c r="D2">
-        <v>58.09999999999999</v>
+        <v>58.33520742394816</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1.541</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.541</v>
       </c>
       <c r="G2">
         <v>96</v>
@@ -1573,28 +1573,28 @@
         <v>11.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07751229999999999</v>
       </c>
       <c r="N2">
-        <v>11.1</v>
+        <v>11.0224877</v>
       </c>
       <c r="O2">
-        <v>3.33</v>
+        <v>3.30674631</v>
       </c>
       <c r="P2">
-        <v>7.77</v>
+        <v>7.71574139</v>
       </c>
       <c r="Q2">
-        <v>20.07</v>
+        <v>20.01574139</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.148416504725415</v>
+        <v>0.1491420759709482</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7205466882059816</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>143.2030787371811</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1480027552112387</v>
+        <v>0.1475890056970625</v>
       </c>
       <c r="C3">
-        <v>152.7942074239482</v>
+        <v>151.4903269789113</v>
       </c>
       <c r="D3">
-        <v>58.33520742394816</v>
+        <v>58.57232697891133</v>
       </c>
       <c r="E3">
-        <v>1.541</v>
+        <v>3.082</v>
       </c>
       <c r="F3">
-        <v>1.541</v>
+        <v>3.082</v>
       </c>
       <c r="G3">
         <v>96</v>
@@ -1655,28 +1655,28 @@
         <v>11.1</v>
       </c>
       <c r="M3">
-        <v>0.07751229999999999</v>
+        <v>0.1550246</v>
       </c>
       <c r="N3">
-        <v>11.0224877</v>
+        <v>10.9449754</v>
       </c>
       <c r="O3">
-        <v>3.30674631</v>
+        <v>3.28349262</v>
       </c>
       <c r="P3">
-        <v>7.71574139</v>
+        <v>7.661482779999999</v>
       </c>
       <c r="Q3">
-        <v>20.01574139</v>
+        <v>19.96148278</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1491420759709482</v>
+        <v>0.1498824547929209</v>
       </c>
       <c r="T3">
-        <v>0.7205466882059816</v>
+        <v>0.7257089370110108</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>143.2030787371811</v>
+        <v>71.60153936859054</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1475890056970625</v>
+        <v>0.1471752561828862</v>
       </c>
       <c r="C4">
-        <v>151.4903269789113</v>
+        <v>150.1883820772084</v>
       </c>
       <c r="D4">
-        <v>58.57232697891133</v>
+        <v>58.81138207720844</v>
       </c>
       <c r="E4">
-        <v>3.082</v>
+        <v>4.622999999999999</v>
       </c>
       <c r="F4">
-        <v>3.082</v>
+        <v>4.622999999999999</v>
       </c>
       <c r="G4">
         <v>96</v>
@@ -1737,28 +1737,28 @@
         <v>11.1</v>
       </c>
       <c r="M4">
-        <v>0.1550246</v>
+        <v>0.2325369</v>
       </c>
       <c r="N4">
-        <v>10.9449754</v>
+        <v>10.8674631</v>
       </c>
       <c r="O4">
-        <v>3.28349262</v>
+        <v>3.26023893</v>
       </c>
       <c r="P4">
-        <v>7.661482779999999</v>
+        <v>7.60722417</v>
       </c>
       <c r="Q4">
-        <v>19.96148278</v>
+        <v>19.90722417</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1498824547929209</v>
+        <v>0.1506380991576147</v>
       </c>
       <c r="T4">
-        <v>0.7257089370110108</v>
+        <v>0.7309776239357313</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.60153936859054</v>
+        <v>47.73435957906037</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1471752561828862</v>
+        <v>0.14676150666871</v>
       </c>
       <c r="C5">
-        <v>150.1883820772084</v>
+        <v>148.8883965149419</v>
       </c>
       <c r="D5">
-        <v>58.81138207720844</v>
+        <v>59.05239651494187</v>
       </c>
       <c r="E5">
-        <v>4.622999999999999</v>
+        <v>6.164</v>
       </c>
       <c r="F5">
-        <v>4.622999999999999</v>
+        <v>6.164</v>
       </c>
       <c r="G5">
         <v>96</v>
@@ -1819,28 +1819,28 @@
         <v>11.1</v>
       </c>
       <c r="M5">
-        <v>0.2325369</v>
+        <v>0.3100492</v>
       </c>
       <c r="N5">
-        <v>10.8674631</v>
+        <v>10.7899508</v>
       </c>
       <c r="O5">
-        <v>3.26023893</v>
+        <v>3.23698524</v>
       </c>
       <c r="P5">
-        <v>7.60722417</v>
+        <v>7.552965560000001</v>
       </c>
       <c r="Q5">
-        <v>19.90722417</v>
+        <v>19.85296556</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1506380991576147</v>
+        <v>0.1514094861132396</v>
       </c>
       <c r="T5">
-        <v>0.7309776239357313</v>
+        <v>0.7363560751713836</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.73435957906037</v>
+        <v>35.80076968429527</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.14676150666871</v>
+        <v>0.1463477571545337</v>
       </c>
       <c r="C6">
-        <v>148.8883965149419</v>
+        <v>147.5903944798935</v>
       </c>
       <c r="D6">
-        <v>59.05239651494187</v>
+        <v>59.29539447989348</v>
       </c>
       <c r="E6">
-        <v>6.164</v>
+        <v>7.705</v>
       </c>
       <c r="F6">
-        <v>6.164</v>
+        <v>7.705</v>
       </c>
       <c r="G6">
         <v>96</v>
@@ -1901,28 +1901,28 @@
         <v>11.1</v>
       </c>
       <c r="M6">
-        <v>0.3100492</v>
+        <v>0.3875615</v>
       </c>
       <c r="N6">
-        <v>10.7899508</v>
+        <v>10.7124385</v>
       </c>
       <c r="O6">
-        <v>3.23698524</v>
+        <v>3.21373155</v>
       </c>
       <c r="P6">
-        <v>7.552965560000001</v>
+        <v>7.498706949999999</v>
       </c>
       <c r="Q6">
-        <v>19.85296556</v>
+        <v>19.79870695</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1514094861132396</v>
+        <v>0.1521971127942461</v>
       </c>
       <c r="T6">
-        <v>0.7363560751713836</v>
+        <v>0.7418477569593653</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.80076968429527</v>
+        <v>28.64061574743621</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1463477571545337</v>
+        <v>0.1459340076403575</v>
       </c>
       <c r="C7">
-        <v>147.5903944798935</v>
+        <v>146.2944005596168</v>
       </c>
       <c r="D7">
-        <v>59.29539447989348</v>
+        <v>59.54040055961678</v>
       </c>
       <c r="E7">
-        <v>7.705</v>
+        <v>9.246</v>
       </c>
       <c r="F7">
-        <v>7.705</v>
+        <v>9.246</v>
       </c>
       <c r="G7">
         <v>96</v>
@@ -1983,28 +1983,28 @@
         <v>11.1</v>
       </c>
       <c r="M7">
-        <v>0.3875615</v>
+        <v>0.4650738</v>
       </c>
       <c r="N7">
-        <v>10.7124385</v>
+        <v>10.6349262</v>
       </c>
       <c r="O7">
-        <v>3.21373155</v>
+        <v>3.19047786</v>
       </c>
       <c r="P7">
-        <v>7.498706949999999</v>
+        <v>7.444448339999999</v>
       </c>
       <c r="Q7">
-        <v>19.79870695</v>
+        <v>19.74444834</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1521971127942461</v>
+        <v>0.153001497489742</v>
       </c>
       <c r="T7">
-        <v>0.7418477569593653</v>
+        <v>0.7474562830407084</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.64061574743621</v>
+        <v>23.86717978953018</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1459340076403575</v>
+        <v>0.1455202581261812</v>
       </c>
       <c r="C8">
-        <v>146.2944005596168</v>
+        <v>145.0004397497302</v>
       </c>
       <c r="D8">
-        <v>59.54040055961678</v>
+        <v>59.78743974973025</v>
       </c>
       <c r="E8">
-        <v>9.245999999999999</v>
+        <v>10.787</v>
       </c>
       <c r="F8">
-        <v>9.245999999999999</v>
+        <v>10.787</v>
       </c>
       <c r="G8">
         <v>96</v>
@@ -2065,28 +2065,28 @@
         <v>11.1</v>
       </c>
       <c r="M8">
-        <v>0.4650737999999999</v>
+        <v>0.5425861</v>
       </c>
       <c r="N8">
-        <v>10.6349262</v>
+        <v>10.5574139</v>
       </c>
       <c r="O8">
-        <v>3.19047786</v>
+        <v>3.16722417</v>
       </c>
       <c r="P8">
-        <v>7.444448339999999</v>
+        <v>7.39018973</v>
       </c>
       <c r="Q8">
-        <v>19.74444834</v>
+        <v>19.69018973</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.153001497489742</v>
+        <v>0.1538231807808401</v>
       </c>
       <c r="T8">
-        <v>0.7474562830407084</v>
+        <v>0.7531854225861665</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.86717978953018</v>
+        <v>20.45758267674016</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1455202581261812</v>
+        <v>0.1451065086120051</v>
       </c>
       <c r="C9">
-        <v>145.0004397497302</v>
+        <v>143.7085374624183</v>
       </c>
       <c r="D9">
-        <v>59.78743974973025</v>
+        <v>60.03653746241833</v>
       </c>
       <c r="E9">
-        <v>10.787</v>
+        <v>12.328</v>
       </c>
       <c r="F9">
-        <v>10.787</v>
+        <v>12.328</v>
       </c>
       <c r="G9">
         <v>96</v>
@@ -2147,28 +2147,28 @@
         <v>11.1</v>
       </c>
       <c r="M9">
-        <v>0.5425861</v>
+        <v>0.6200983999999999</v>
       </c>
       <c r="N9">
-        <v>10.5574139</v>
+        <v>10.4799016</v>
       </c>
       <c r="O9">
-        <v>3.16722417</v>
+        <v>3.14397048</v>
       </c>
       <c r="P9">
-        <v>7.39018973</v>
+        <v>7.33593112</v>
       </c>
       <c r="Q9">
-        <v>19.69018973</v>
+        <v>19.63593112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1538231807808401</v>
+        <v>0.1546627267521794</v>
       </c>
       <c r="T9">
-        <v>0.7531854225861665</v>
+        <v>0.7590391086434822</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.45758267674016</v>
+        <v>17.90038484214763</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1451065086120051</v>
+        <v>0.1446927590978288</v>
       </c>
       <c r="C10">
-        <v>143.7085374624183</v>
+        <v>142.4187195351455</v>
       </c>
       <c r="D10">
-        <v>60.03653746241833</v>
+        <v>60.28771953514551</v>
       </c>
       <c r="E10">
-        <v>12.328</v>
+        <v>13.869</v>
       </c>
       <c r="F10">
-        <v>12.328</v>
+        <v>13.869</v>
       </c>
       <c r="G10">
         <v>96</v>
@@ -2229,28 +2229,28 @@
         <v>11.1</v>
       </c>
       <c r="M10">
-        <v>0.6200983999999999</v>
+        <v>0.6976106999999999</v>
       </c>
       <c r="N10">
-        <v>10.4799016</v>
+        <v>10.4023893</v>
       </c>
       <c r="O10">
-        <v>3.14397048</v>
+        <v>3.12071679</v>
       </c>
       <c r="P10">
-        <v>7.33593112</v>
+        <v>7.28167251</v>
       </c>
       <c r="Q10">
-        <v>19.63593112</v>
+        <v>19.58167251</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1546627267521794</v>
+        <v>0.1555207242833283</v>
       </c>
       <c r="T10">
-        <v>0.7590391086434822</v>
+        <v>0.7650214471416181</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.90038484214763</v>
+        <v>15.91145319302012</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1446927590978288</v>
+        <v>0.1442790095836525</v>
       </c>
       <c r="C11">
-        <v>142.4187195351455</v>
+        <v>141.13101223959</v>
       </c>
       <c r="D11">
-        <v>60.28771953514551</v>
+        <v>60.54101223959001</v>
       </c>
       <c r="E11">
-        <v>13.869</v>
+        <v>15.41</v>
       </c>
       <c r="F11">
-        <v>13.869</v>
+        <v>15.41</v>
       </c>
       <c r="G11">
         <v>96</v>
@@ -2311,28 +2311,28 @@
         <v>11.1</v>
       </c>
       <c r="M11">
-        <v>0.6976106999999999</v>
+        <v>0.7751229999999999</v>
       </c>
       <c r="N11">
-        <v>10.4023893</v>
+        <v>10.324877</v>
       </c>
       <c r="O11">
-        <v>3.12071679</v>
+        <v>3.0974631</v>
       </c>
       <c r="P11">
-        <v>7.28167251</v>
+        <v>7.227413899999999</v>
       </c>
       <c r="Q11">
-        <v>19.58167251</v>
+        <v>19.5274139</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1555207242833283</v>
+        <v>0.1563977884262806</v>
       </c>
       <c r="T11">
-        <v>0.7650214471416181</v>
+        <v>0.7711367264952681</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.91145319302012</v>
+        <v>14.32030787371811</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1442790095836525</v>
+        <v>0.1438652600694763</v>
       </c>
       <c r="C12">
-        <v>141.13101223959</v>
+        <v>139.8454422908041</v>
       </c>
       <c r="D12">
-        <v>60.54101223959001</v>
+        <v>60.79644229080412</v>
       </c>
       <c r="E12">
-        <v>15.41</v>
+        <v>16.951</v>
       </c>
       <c r="F12">
-        <v>15.41</v>
+        <v>16.951</v>
       </c>
       <c r="G12">
         <v>96</v>
@@ -2393,28 +2393,28 @@
         <v>11.1</v>
       </c>
       <c r="M12">
-        <v>0.775123</v>
+        <v>0.8526353</v>
       </c>
       <c r="N12">
-        <v>10.324877</v>
+        <v>10.2473647</v>
       </c>
       <c r="O12">
-        <v>3.0974631</v>
+        <v>3.07420941</v>
       </c>
       <c r="P12">
-        <v>7.227413899999999</v>
+        <v>7.17315529</v>
       </c>
       <c r="Q12">
-        <v>19.5274139</v>
+        <v>19.47315529</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1563977884262806</v>
+        <v>0.157294561875816</v>
       </c>
       <c r="T12">
-        <v>0.7711367264952681</v>
+        <v>0.7773894278568653</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.32030787371811</v>
+        <v>13.0184617033801</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1438652600694763</v>
+        <v>0.1435775105553</v>
       </c>
       <c r="C13">
-        <v>139.8454422908041</v>
+        <v>138.4833601895466</v>
       </c>
       <c r="D13">
-        <v>60.79644229080412</v>
+        <v>60.97536018954655</v>
       </c>
       <c r="E13">
-        <v>16.951</v>
+        <v>18.492</v>
       </c>
       <c r="F13">
-        <v>16.951</v>
+        <v>18.492</v>
       </c>
       <c r="G13">
         <v>96</v>
@@ -2475,45 +2475,45 @@
         <v>11.1</v>
       </c>
       <c r="M13">
-        <v>0.8526353</v>
+        <v>0.9578855999999999</v>
       </c>
       <c r="N13">
-        <v>10.2473647</v>
+        <v>10.1421144</v>
       </c>
       <c r="O13">
-        <v>3.07420941</v>
+        <v>3.04263432</v>
       </c>
       <c r="P13">
-        <v>7.17315529</v>
+        <v>7.099480080000001</v>
       </c>
       <c r="Q13">
-        <v>19.47315529</v>
+        <v>19.39948008</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.157294561875816</v>
+        <v>0.1582117165401137</v>
       </c>
       <c r="T13">
-        <v>0.7773894278568653</v>
+        <v>0.7837842360675897</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.0184617033801</v>
+        <v>11.58802261982015</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1435775105553</v>
+        <v>0.1431742610411238</v>
       </c>
       <c r="C14">
-        <v>138.4833601895466</v>
+        <v>137.1948733702399</v>
       </c>
       <c r="D14">
-        <v>60.97536018954655</v>
+        <v>61.22787337023989</v>
       </c>
       <c r="E14">
-        <v>18.492</v>
+        <v>20.033</v>
       </c>
       <c r="F14">
-        <v>18.492</v>
+        <v>20.033</v>
       </c>
       <c r="G14">
         <v>96</v>
@@ -2557,28 +2557,28 @@
         <v>11.1</v>
       </c>
       <c r="M14">
-        <v>0.9578855999999999</v>
+        <v>1.0377094</v>
       </c>
       <c r="N14">
-        <v>10.1421144</v>
+        <v>10.0622906</v>
       </c>
       <c r="O14">
-        <v>3.04263432</v>
+        <v>3.01868718</v>
       </c>
       <c r="P14">
-        <v>7.099480080000001</v>
+        <v>7.043603419999999</v>
       </c>
       <c r="Q14">
-        <v>19.39948008</v>
+        <v>19.34360342</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1582117165401137</v>
+        <v>0.1591499552196825</v>
       </c>
       <c r="T14">
-        <v>0.7837842360675897</v>
+        <v>0.7903260513636182</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.58802261982015</v>
+        <v>10.69663626444937</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1431742610411238</v>
+        <v>0.1427710115269475</v>
       </c>
       <c r="C15">
-        <v>137.1948733702399</v>
+        <v>135.9084866799477</v>
       </c>
       <c r="D15">
-        <v>61.22787337023989</v>
+        <v>61.48248667994773</v>
       </c>
       <c r="E15">
-        <v>20.033</v>
+        <v>21.574</v>
       </c>
       <c r="F15">
-        <v>20.033</v>
+        <v>21.574</v>
       </c>
       <c r="G15">
         <v>96</v>
@@ -2639,28 +2639,28 @@
         <v>11.1</v>
       </c>
       <c r="M15">
-        <v>1.0377094</v>
+        <v>1.1175332</v>
       </c>
       <c r="N15">
-        <v>10.0622906</v>
+        <v>9.982466799999999</v>
       </c>
       <c r="O15">
-        <v>3.01868718</v>
+        <v>2.994740039999999</v>
       </c>
       <c r="P15">
-        <v>7.043603419999999</v>
+        <v>6.987726759999999</v>
       </c>
       <c r="Q15">
-        <v>19.34360342</v>
+        <v>19.28772676</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1591499552196825</v>
+        <v>0.1601100134034274</v>
       </c>
       <c r="T15">
-        <v>0.7903260513636182</v>
+        <v>0.7970200018990892</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.69663626444937</v>
+        <v>9.932590816988702</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1427710115269475</v>
+        <v>0.1425462620127713</v>
       </c>
       <c r="C16">
-        <v>135.9084866799477</v>
+        <v>134.5103155471741</v>
       </c>
       <c r="D16">
-        <v>61.48248667994773</v>
+        <v>61.62531554717405</v>
       </c>
       <c r="E16">
-        <v>21.574</v>
+        <v>23.115</v>
       </c>
       <c r="F16">
-        <v>21.574</v>
+        <v>23.115</v>
       </c>
       <c r="G16">
         <v>96</v>
@@ -2721,45 +2721,45 @@
         <v>11.1</v>
       </c>
       <c r="M16">
-        <v>1.1175332</v>
+        <v>1.2366525</v>
       </c>
       <c r="N16">
-        <v>9.982466799999999</v>
+        <v>9.8633475</v>
       </c>
       <c r="O16">
-        <v>2.994740039999999</v>
+        <v>2.95900425</v>
       </c>
       <c r="P16">
-        <v>6.987726759999999</v>
+        <v>6.90434325</v>
       </c>
       <c r="Q16">
-        <v>19.28772676</v>
+        <v>19.20434325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1601100134034274</v>
+        <v>0.1610926611914957</v>
       </c>
       <c r="T16">
-        <v>0.7970200018990892</v>
+        <v>0.8038714571530418</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.932590816988702</v>
+        <v>8.975844062903684</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1425462620127713</v>
+        <v>0.142154912498595</v>
       </c>
       <c r="C17">
-        <v>134.5103155471741</v>
+        <v>133.2196093482368</v>
       </c>
       <c r="D17">
-        <v>61.62531554717405</v>
+        <v>61.87560934823683</v>
       </c>
       <c r="E17">
-        <v>23.115</v>
+        <v>24.656</v>
       </c>
       <c r="F17">
-        <v>23.115</v>
+        <v>24.656</v>
       </c>
       <c r="G17">
         <v>96</v>
@@ -2803,28 +2803,28 @@
         <v>11.1</v>
       </c>
       <c r="M17">
-        <v>1.2366525</v>
+        <v>1.319096</v>
       </c>
       <c r="N17">
-        <v>9.8633475</v>
+        <v>9.780904</v>
       </c>
       <c r="O17">
-        <v>2.95900425</v>
+        <v>2.9342712</v>
       </c>
       <c r="P17">
-        <v>6.90434325</v>
+        <v>6.8466328</v>
       </c>
       <c r="Q17">
-        <v>19.20434325</v>
+        <v>19.1466328</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1610926611914957</v>
+        <v>0.1620987053554703</v>
       </c>
       <c r="T17">
-        <v>0.8038714571530418</v>
+        <v>0.8108860422939933</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.975844062903686</v>
+        <v>8.414853808972206</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.142154912498595</v>
+        <v>0.1417635629844188</v>
       </c>
       <c r="C18">
-        <v>133.2196093482368</v>
+        <v>131.9309445982496</v>
       </c>
       <c r="D18">
-        <v>61.87560934823683</v>
+        <v>62.12794459824962</v>
       </c>
       <c r="E18">
-        <v>24.656</v>
+        <v>26.197</v>
       </c>
       <c r="F18">
-        <v>24.656</v>
+        <v>26.197</v>
       </c>
       <c r="G18">
         <v>96</v>
@@ -2885,28 +2885,28 @@
         <v>11.1</v>
       </c>
       <c r="M18">
-        <v>1.319096</v>
+        <v>1.4015395</v>
       </c>
       <c r="N18">
-        <v>9.780904</v>
+        <v>9.698460499999999</v>
       </c>
       <c r="O18">
-        <v>2.9342712</v>
+        <v>2.90953815</v>
       </c>
       <c r="P18">
-        <v>6.8466328</v>
+        <v>6.78892235</v>
       </c>
       <c r="Q18">
-        <v>19.1466328</v>
+        <v>19.08892235</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1620987053554703</v>
+        <v>0.1631289915474926</v>
       </c>
       <c r="T18">
-        <v>0.8108860422939933</v>
+        <v>0.8180696535829196</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.414853808972206</v>
+        <v>7.919862408444429</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1417635629844188</v>
+        <v>0.1414730134702426</v>
       </c>
       <c r="C19">
-        <v>131.9309445982496</v>
+        <v>130.5786210438327</v>
       </c>
       <c r="D19">
-        <v>62.12794459824962</v>
+        <v>62.31662104383273</v>
       </c>
       <c r="E19">
-        <v>26.197</v>
+        <v>27.738</v>
       </c>
       <c r="F19">
-        <v>26.197</v>
+        <v>27.738</v>
       </c>
       <c r="G19">
         <v>96</v>
@@ -2967,45 +2967,45 @@
         <v>11.1</v>
       </c>
       <c r="M19">
-        <v>1.4015395</v>
+        <v>1.5061734</v>
       </c>
       <c r="N19">
-        <v>9.698460499999999</v>
+        <v>9.5938266</v>
       </c>
       <c r="O19">
-        <v>2.90953815</v>
+        <v>2.87814798</v>
       </c>
       <c r="P19">
-        <v>6.78892235</v>
+        <v>6.71567862</v>
       </c>
       <c r="Q19">
-        <v>19.08892235</v>
+        <v>19.01567862</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1631289915474926</v>
+        <v>0.1641844066710275</v>
       </c>
       <c r="T19">
-        <v>0.8180696535829196</v>
+        <v>0.825428474903283</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.919862408444429</v>
+        <v>7.369669388664013</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1414730134702426</v>
+        <v>0.1410872639560663</v>
       </c>
       <c r="C20">
-        <v>130.5786210438327</v>
+        <v>129.2898961674405</v>
       </c>
       <c r="D20">
-        <v>62.31662104383273</v>
+        <v>62.5688961674405</v>
       </c>
       <c r="E20">
-        <v>27.738</v>
+        <v>29.279</v>
       </c>
       <c r="F20">
-        <v>27.738</v>
+        <v>29.279</v>
       </c>
       <c r="G20">
         <v>96</v>
@@ -3049,28 +3049,28 @@
         <v>11.1</v>
       </c>
       <c r="M20">
-        <v>1.5061734</v>
+        <v>1.5898497</v>
       </c>
       <c r="N20">
-        <v>9.5938266</v>
+        <v>9.510150299999999</v>
       </c>
       <c r="O20">
-        <v>2.87814798</v>
+        <v>2.85304509</v>
       </c>
       <c r="P20">
-        <v>6.71567862</v>
+        <v>6.657105209999999</v>
       </c>
       <c r="Q20">
-        <v>19.01567862</v>
+        <v>18.95710521</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1641844066710275</v>
+        <v>0.1652658814272424</v>
       </c>
       <c r="T20">
-        <v>0.825428474903283</v>
+        <v>0.8329689955155072</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.369669388664014</v>
+        <v>6.981792052418539</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1410872639560663</v>
+        <v>0.1407015144418901</v>
       </c>
       <c r="C21">
-        <v>129.2898961674405</v>
+        <v>128.0032221541339</v>
       </c>
       <c r="D21">
-        <v>62.5688961674405</v>
+        <v>62.82322215413394</v>
       </c>
       <c r="E21">
-        <v>29.279</v>
+        <v>30.82</v>
       </c>
       <c r="F21">
-        <v>29.279</v>
+        <v>30.82</v>
       </c>
       <c r="G21">
         <v>96</v>
@@ -3131,28 +3131,28 @@
         <v>11.1</v>
       </c>
       <c r="M21">
-        <v>1.5898497</v>
+        <v>1.673526</v>
       </c>
       <c r="N21">
-        <v>9.510150299999999</v>
+        <v>9.426473999999999</v>
       </c>
       <c r="O21">
-        <v>2.85304509</v>
+        <v>2.827942199999999</v>
       </c>
       <c r="P21">
-        <v>6.657105209999999</v>
+        <v>6.5985318</v>
       </c>
       <c r="Q21">
-        <v>18.95710521</v>
+        <v>18.8985318</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1652658814272424</v>
+        <v>0.1663743930523626</v>
       </c>
       <c r="T21">
-        <v>0.8329689955155072</v>
+        <v>0.8406980291430372</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.981792052418539</v>
+        <v>6.632702449797612</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1407015144418901</v>
+        <v>0.1403157649277138</v>
       </c>
       <c r="C22">
-        <v>128.0032221541339</v>
+        <v>126.7186241146267</v>
       </c>
       <c r="D22">
-        <v>62.82322215413394</v>
+        <v>63.07962411462675</v>
       </c>
       <c r="E22">
-        <v>30.82</v>
+        <v>32.361</v>
       </c>
       <c r="F22">
-        <v>30.82</v>
+        <v>32.361</v>
       </c>
       <c r="G22">
         <v>96</v>
@@ -3213,28 +3213,28 @@
         <v>11.1</v>
       </c>
       <c r="M22">
-        <v>1.673526</v>
+        <v>1.7572023</v>
       </c>
       <c r="N22">
-        <v>9.426473999999999</v>
+        <v>9.342797699999998</v>
       </c>
       <c r="O22">
-        <v>2.827942199999999</v>
+        <v>2.80283931</v>
       </c>
       <c r="P22">
-        <v>6.5985318</v>
+        <v>6.539958389999999</v>
       </c>
       <c r="Q22">
-        <v>18.8985318</v>
+        <v>18.83995839</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1663743930523626</v>
+        <v>0.1675109682629289</v>
       </c>
       <c r="T22">
-        <v>0.8406980291430372</v>
+        <v>0.848622734507973</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.632702449797612</v>
+        <v>6.316859475997725</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1403157649277138</v>
+        <v>0.1400840154135376</v>
       </c>
       <c r="C23">
-        <v>126.7186241146268</v>
+        <v>125.3326734321475</v>
       </c>
       <c r="D23">
-        <v>63.07962411462676</v>
+        <v>63.2346734321475</v>
       </c>
       <c r="E23">
-        <v>32.361</v>
+        <v>33.902</v>
       </c>
       <c r="F23">
-        <v>32.361</v>
+        <v>33.902</v>
       </c>
       <c r="G23">
         <v>96</v>
@@ -3295,45 +3295,45 @@
         <v>11.1</v>
       </c>
       <c r="M23">
-        <v>1.7572023</v>
+        <v>1.8747806</v>
       </c>
       <c r="N23">
-        <v>9.3427977</v>
+        <v>9.2252194</v>
       </c>
       <c r="O23">
-        <v>2.80283931</v>
+        <v>2.76756582</v>
       </c>
       <c r="P23">
-        <v>6.539958390000001</v>
+        <v>6.457653580000001</v>
       </c>
       <c r="Q23">
-        <v>18.83995839</v>
+        <v>18.75765358</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1675109682629289</v>
+        <v>0.1686766864276123</v>
       </c>
       <c r="T23">
-        <v>0.8486227345079728</v>
+        <v>0.8567506374463685</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.316859475997727</v>
+        <v>5.920692800000171</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1400840154135376</v>
+        <v>0.1397052658993613</v>
       </c>
       <c r="C24">
-        <v>125.3326734321475</v>
+        <v>124.0467187867625</v>
       </c>
       <c r="D24">
-        <v>63.2346734321475</v>
+        <v>63.48971878676251</v>
       </c>
       <c r="E24">
-        <v>33.902</v>
+        <v>35.443</v>
       </c>
       <c r="F24">
-        <v>33.902</v>
+        <v>35.443</v>
       </c>
       <c r="G24">
         <v>96</v>
@@ -3377,28 +3377,28 @@
         <v>11.1</v>
       </c>
       <c r="M24">
-        <v>1.8747806</v>
+        <v>1.9599979</v>
       </c>
       <c r="N24">
-        <v>9.2252194</v>
+        <v>9.1400021</v>
       </c>
       <c r="O24">
-        <v>2.76756582</v>
+        <v>2.74200063</v>
       </c>
       <c r="P24">
-        <v>6.457653580000001</v>
+        <v>6.398001470000001</v>
       </c>
       <c r="Q24">
-        <v>18.75765358</v>
+        <v>18.69800147</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1686766864276123</v>
+        <v>0.1698726829861835</v>
       </c>
       <c r="T24">
-        <v>0.8567506374463685</v>
+        <v>0.8650896547468002</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.920692800000171</v>
+        <v>5.663271373913207</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1397052658993613</v>
+        <v>0.1393265163851851</v>
       </c>
       <c r="C25">
-        <v>124.0467187867625</v>
+        <v>122.7628298294387</v>
       </c>
       <c r="D25">
-        <v>63.48971878676251</v>
+        <v>63.74682982943875</v>
       </c>
       <c r="E25">
-        <v>35.443</v>
+        <v>36.984</v>
       </c>
       <c r="F25">
-        <v>35.443</v>
+        <v>36.984</v>
       </c>
       <c r="G25">
         <v>96</v>
@@ -3459,28 +3459,28 @@
         <v>11.1</v>
       </c>
       <c r="M25">
-        <v>1.9599979</v>
+        <v>2.0452152</v>
       </c>
       <c r="N25">
-        <v>9.1400021</v>
+        <v>9.0547848</v>
       </c>
       <c r="O25">
-        <v>2.74200063</v>
+        <v>2.71643544</v>
       </c>
       <c r="P25">
-        <v>6.398001470000001</v>
+        <v>6.33834936</v>
       </c>
       <c r="Q25">
-        <v>18.69800147</v>
+        <v>18.63834936</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1698726829861835</v>
+        <v>0.1711001531384014</v>
       </c>
       <c r="T25">
-        <v>0.8650896547468002</v>
+        <v>0.8736481198709277</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.663271373913207</v>
+        <v>5.427301733333489</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1393265163851851</v>
+        <v>0.1389477668710089</v>
       </c>
       <c r="C26">
-        <v>122.7628298294388</v>
+        <v>121.4810317581507</v>
       </c>
       <c r="D26">
-        <v>63.74682982943875</v>
+        <v>64.00603175815068</v>
       </c>
       <c r="E26">
-        <v>36.98399999999999</v>
+        <v>38.525</v>
       </c>
       <c r="F26">
-        <v>36.98399999999999</v>
+        <v>38.525</v>
       </c>
       <c r="G26">
         <v>96</v>
@@ -3541,28 +3541,28 @@
         <v>11.1</v>
       </c>
       <c r="M26">
-        <v>2.0452152</v>
+        <v>2.1304325</v>
       </c>
       <c r="N26">
-        <v>9.0547848</v>
+        <v>8.9695675</v>
       </c>
       <c r="O26">
-        <v>2.71643544</v>
+        <v>2.69087025</v>
       </c>
       <c r="P26">
-        <v>6.33834936</v>
+        <v>6.27869725</v>
       </c>
       <c r="Q26">
-        <v>18.63834936</v>
+        <v>18.57869725</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1711001531384014</v>
+        <v>0.1723603558280118</v>
       </c>
       <c r="T26">
-        <v>0.8736481198709277</v>
+        <v>0.8824348107316986</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.42730173333349</v>
+        <v>5.210209664000151</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1389477668710089</v>
+        <v>0.1385690173568326</v>
       </c>
       <c r="C27">
-        <v>121.4810317581507</v>
+        <v>120.2013501823774</v>
       </c>
       <c r="D27">
-        <v>64.00603175815068</v>
+        <v>64.26735018237741</v>
       </c>
       <c r="E27">
-        <v>38.525</v>
+        <v>40.066</v>
       </c>
       <c r="F27">
-        <v>38.525</v>
+        <v>40.066</v>
       </c>
       <c r="G27">
         <v>96</v>
@@ -3623,28 +3623,28 @@
         <v>11.1</v>
       </c>
       <c r="M27">
-        <v>2.1304325</v>
+        <v>2.2156498</v>
       </c>
       <c r="N27">
-        <v>8.9695675</v>
+        <v>8.8843502</v>
       </c>
       <c r="O27">
-        <v>2.69087025</v>
+        <v>2.66530506</v>
       </c>
       <c r="P27">
-        <v>6.27869725</v>
+        <v>6.21904514</v>
       </c>
       <c r="Q27">
-        <v>18.57869725</v>
+        <v>18.51904514</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1723603558280118</v>
+        <v>0.1736546180497738</v>
       </c>
       <c r="T27">
-        <v>0.8824348107316986</v>
+        <v>0.8914589797238416</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.210209664000151</v>
+        <v>5.009816984615529</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1385690173568326</v>
+        <v>0.1381902678426564</v>
       </c>
       <c r="C28">
-        <v>120.2013501823774</v>
+        <v>118.9238111315374</v>
       </c>
       <c r="D28">
-        <v>64.26735018237741</v>
+        <v>64.53081113153739</v>
       </c>
       <c r="E28">
-        <v>40.066</v>
+        <v>41.607</v>
       </c>
       <c r="F28">
-        <v>40.066</v>
+        <v>41.607</v>
       </c>
       <c r="G28">
         <v>96</v>
@@ -3705,28 +3705,28 @@
         <v>11.1</v>
       </c>
       <c r="M28">
-        <v>2.2156498</v>
+        <v>2.3008671</v>
       </c>
       <c r="N28">
-        <v>8.8843502</v>
+        <v>8.7991329</v>
       </c>
       <c r="O28">
-        <v>2.66530506</v>
+        <v>2.63973987</v>
       </c>
       <c r="P28">
-        <v>6.21904514</v>
+        <v>6.15939303</v>
       </c>
       <c r="Q28">
-        <v>18.51904514</v>
+        <v>18.45939303</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1736546180497738</v>
+        <v>0.1749843395104882</v>
       </c>
       <c r="T28">
-        <v>0.8914589797238416</v>
+        <v>0.9007303862226187</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.009816984615529</v>
+        <v>4.824268207407546</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1381902678426564</v>
+        <v>0.1378115183284801</v>
       </c>
       <c r="C29">
-        <v>118.9238111315374</v>
+        <v>117.6484410636315</v>
       </c>
       <c r="D29">
-        <v>64.53081113153739</v>
+        <v>64.79644106363149</v>
       </c>
       <c r="E29">
-        <v>41.607</v>
+        <v>43.148</v>
       </c>
       <c r="F29">
-        <v>41.607</v>
+        <v>43.148</v>
       </c>
       <c r="G29">
         <v>96</v>
@@ -3787,28 +3787,28 @@
         <v>11.1</v>
       </c>
       <c r="M29">
-        <v>2.3008671</v>
+        <v>2.3860844</v>
       </c>
       <c r="N29">
-        <v>8.7991329</v>
+        <v>8.7139156</v>
       </c>
       <c r="O29">
-        <v>2.63973987</v>
+        <v>2.61417468</v>
       </c>
       <c r="P29">
-        <v>6.15939303</v>
+        <v>6.09974092</v>
       </c>
       <c r="Q29">
-        <v>18.45939303</v>
+        <v>18.39974092</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1749843395104882</v>
+        <v>0.1763509976784446</v>
       </c>
       <c r="T29">
-        <v>0.9007303862226187</v>
+        <v>0.9102593317908061</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.824268207407546</v>
+        <v>4.651972914285848</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1378115183284801</v>
+        <v>0.1379402688143039</v>
       </c>
       <c r="C30">
-        <v>117.6484410636315</v>
+        <v>116.0168989654376</v>
       </c>
       <c r="D30">
-        <v>64.79644106363149</v>
+        <v>64.70589896543763</v>
       </c>
       <c r="E30">
-        <v>43.148</v>
+        <v>44.68900000000001</v>
       </c>
       <c r="F30">
-        <v>43.148</v>
+        <v>44.68900000000001</v>
       </c>
       <c r="G30">
         <v>96</v>
@@ -3869,45 +3869,45 @@
         <v>11.1</v>
       </c>
       <c r="M30">
-        <v>2.3860844</v>
+        <v>2.583024200000001</v>
       </c>
       <c r="N30">
-        <v>8.7139156</v>
+        <v>8.516975799999999</v>
       </c>
       <c r="O30">
-        <v>2.61417468</v>
+        <v>2.55509274</v>
       </c>
       <c r="P30">
-        <v>6.09974092</v>
+        <v>5.96188306</v>
       </c>
       <c r="Q30">
-        <v>18.39974092</v>
+        <v>18.26188306</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1763509976784446</v>
+        <v>0.1777561532595829</v>
       </c>
       <c r="T30">
-        <v>0.9102593317908061</v>
+        <v>0.9200566983609145</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.651972914285848</v>
+        <v>4.297288426488609</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1379402688143039</v>
+        <v>0.1375790193001276</v>
       </c>
       <c r="C31">
-        <v>116.0168989654376</v>
+        <v>114.7305865263187</v>
       </c>
       <c r="D31">
-        <v>64.70589896543763</v>
+        <v>64.96058652631865</v>
       </c>
       <c r="E31">
-        <v>44.68899999999999</v>
+        <v>46.23</v>
       </c>
       <c r="F31">
-        <v>44.68899999999999</v>
+        <v>46.23</v>
       </c>
       <c r="G31">
         <v>96</v>
@@ -3951,28 +3951,28 @@
         <v>11.1</v>
       </c>
       <c r="M31">
-        <v>2.5830242</v>
+        <v>2.672094</v>
       </c>
       <c r="N31">
-        <v>8.516975800000001</v>
+        <v>8.427906</v>
       </c>
       <c r="O31">
-        <v>2.55509274</v>
+        <v>2.5283718</v>
       </c>
       <c r="P31">
-        <v>5.961883060000001</v>
+        <v>5.8995342</v>
       </c>
       <c r="Q31">
-        <v>18.26188306</v>
+        <v>18.1995342</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1777561532595829</v>
+        <v>0.1792014561430395</v>
       </c>
       <c r="T31">
-        <v>0.9200566983609145</v>
+        <v>0.9301339896901688</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.297288426488611</v>
+        <v>4.15404547893899</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1375790193001276</v>
+        <v>0.1372177697859513</v>
       </c>
       <c r="C32">
-        <v>114.7305865263187</v>
+        <v>113.4462869509536</v>
       </c>
       <c r="D32">
-        <v>64.96058652631865</v>
+        <v>65.21728695095365</v>
       </c>
       <c r="E32">
-        <v>46.23</v>
+        <v>47.771</v>
       </c>
       <c r="F32">
-        <v>46.23</v>
+        <v>47.771</v>
       </c>
       <c r="G32">
         <v>96</v>
@@ -4033,28 +4033,28 @@
         <v>11.1</v>
       </c>
       <c r="M32">
-        <v>2.672094</v>
+        <v>2.7611638</v>
       </c>
       <c r="N32">
-        <v>8.427906</v>
+        <v>8.338836199999999</v>
       </c>
       <c r="O32">
-        <v>2.5283718</v>
+        <v>2.50165086</v>
       </c>
       <c r="P32">
-        <v>5.8995342</v>
+        <v>5.83718534</v>
       </c>
       <c r="Q32">
-        <v>18.1995342</v>
+        <v>18.13718534</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1792014561430395</v>
+        <v>0.1806886518636976</v>
       </c>
       <c r="T32">
-        <v>0.9301339896901688</v>
+        <v>0.9405033764202709</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.15404547893899</v>
+        <v>4.020044011876441</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1372177697859513</v>
+        <v>0.1376405202717751</v>
       </c>
       <c r="C33">
-        <v>113.4462869509536</v>
+        <v>111.6050856927178</v>
       </c>
       <c r="D33">
-        <v>65.21728695095365</v>
+        <v>64.91708569271778</v>
       </c>
       <c r="E33">
-        <v>47.771</v>
+        <v>49.312</v>
       </c>
       <c r="F33">
-        <v>47.771</v>
+        <v>49.312</v>
       </c>
       <c r="G33">
         <v>96</v>
@@ -4115,45 +4115,45 @@
         <v>11.1</v>
       </c>
       <c r="M33">
-        <v>2.7611638</v>
+        <v>3.0228256</v>
       </c>
       <c r="N33">
-        <v>8.338836199999999</v>
+        <v>8.077174400000001</v>
       </c>
       <c r="O33">
-        <v>2.50165086</v>
+        <v>2.42315232</v>
       </c>
       <c r="P33">
-        <v>5.83718534</v>
+        <v>5.654022080000001</v>
       </c>
       <c r="Q33">
-        <v>18.13718534</v>
+        <v>17.95402208</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1806886518636976</v>
+        <v>0.1822195886349634</v>
       </c>
       <c r="T33">
-        <v>0.9405033764202709</v>
+        <v>0.9511777451130232</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.020044011876441</v>
+        <v>3.672061001468295</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1376405202717751</v>
+        <v>0.1373037707575989</v>
       </c>
       <c r="C34">
-        <v>111.6050856927178</v>
+        <v>110.3029916622507</v>
       </c>
       <c r="D34">
-        <v>64.91708569271778</v>
+        <v>65.15599166225067</v>
       </c>
       <c r="E34">
-        <v>49.312</v>
+        <v>50.853</v>
       </c>
       <c r="F34">
-        <v>49.312</v>
+        <v>50.853</v>
       </c>
       <c r="G34">
         <v>96</v>
@@ -4197,28 +4197,28 @@
         <v>11.1</v>
       </c>
       <c r="M34">
-        <v>3.0228256</v>
+        <v>3.1172889</v>
       </c>
       <c r="N34">
-        <v>8.077174400000001</v>
+        <v>7.9827111</v>
       </c>
       <c r="O34">
-        <v>2.42315232</v>
+        <v>2.39481333</v>
       </c>
       <c r="P34">
-        <v>5.654022080000001</v>
+        <v>5.58789777</v>
       </c>
       <c r="Q34">
-        <v>17.95402208</v>
+        <v>17.88789777</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1822195886349634</v>
+        <v>0.1837962250113417</v>
       </c>
       <c r="T34">
-        <v>0.9511777451130232</v>
+        <v>0.9621707516772011</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.672061001468295</v>
+        <v>3.560786425666225</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1373037707575989</v>
+        <v>0.1376334212434226</v>
       </c>
       <c r="C35">
-        <v>110.3029916622507</v>
+        <v>108.528103998969</v>
       </c>
       <c r="D35">
-        <v>65.15599166225067</v>
+        <v>64.92210399896895</v>
       </c>
       <c r="E35">
-        <v>50.853</v>
+        <v>52.394</v>
       </c>
       <c r="F35">
-        <v>50.853</v>
+        <v>52.394</v>
       </c>
       <c r="G35">
         <v>96</v>
@@ -4279,45 +4279,45 @@
         <v>11.1</v>
       </c>
       <c r="M35">
-        <v>3.1172889</v>
+        <v>3.3584554</v>
       </c>
       <c r="N35">
-        <v>7.9827111</v>
+        <v>7.741544599999999</v>
       </c>
       <c r="O35">
-        <v>2.39481333</v>
+        <v>2.32246338</v>
       </c>
       <c r="P35">
-        <v>5.58789777</v>
+        <v>5.419081219999999</v>
       </c>
       <c r="Q35">
-        <v>17.88789777</v>
+        <v>17.71908122</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1837962250113417</v>
+        <v>0.1854206382476101</v>
       </c>
       <c r="T35">
-        <v>0.9621707516772011</v>
+        <v>0.9734968796524144</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.560786425666225</v>
+        <v>3.305090786675327</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1376334212434226</v>
+        <v>0.1373162717292464</v>
       </c>
       <c r="C36">
-        <v>108.528103998969</v>
+        <v>107.212091461346</v>
       </c>
       <c r="D36">
-        <v>64.92210399896895</v>
+        <v>65.14709146134604</v>
       </c>
       <c r="E36">
-        <v>52.394</v>
+        <v>53.935</v>
       </c>
       <c r="F36">
-        <v>52.394</v>
+        <v>53.935</v>
       </c>
       <c r="G36">
         <v>96</v>
@@ -4361,28 +4361,28 @@
         <v>11.1</v>
       </c>
       <c r="M36">
-        <v>3.3584554</v>
+        <v>3.457233500000001</v>
       </c>
       <c r="N36">
-        <v>7.741544599999999</v>
+        <v>7.642766499999999</v>
       </c>
       <c r="O36">
-        <v>2.32246338</v>
+        <v>2.292829949999999</v>
       </c>
       <c r="P36">
-        <v>5.419081219999999</v>
+        <v>5.349936549999999</v>
       </c>
       <c r="Q36">
-        <v>17.71908122</v>
+        <v>17.64993655</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1854206382476101</v>
+        <v>0.1870950334296098</v>
       </c>
       <c r="T36">
-        <v>0.9734968796524144</v>
+        <v>0.985171503873019</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.305090786675327</v>
+        <v>3.210659621341745</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1373162717292464</v>
+        <v>0.1369991222150701</v>
       </c>
       <c r="C37">
-        <v>107.212091461346</v>
+        <v>105.8976437340558</v>
       </c>
       <c r="D37">
-        <v>65.14709146134604</v>
+        <v>65.37364373405582</v>
       </c>
       <c r="E37">
-        <v>53.935</v>
+        <v>55.47600000000001</v>
       </c>
       <c r="F37">
-        <v>53.935</v>
+        <v>55.47600000000001</v>
       </c>
       <c r="G37">
         <v>96</v>
@@ -4443,28 +4443,28 @@
         <v>11.1</v>
       </c>
       <c r="M37">
-        <v>3.457233500000001</v>
+        <v>3.556011600000001</v>
       </c>
       <c r="N37">
-        <v>7.642766499999999</v>
+        <v>7.543988399999999</v>
       </c>
       <c r="O37">
-        <v>2.292829949999999</v>
+        <v>2.26319652</v>
       </c>
       <c r="P37">
-        <v>5.349936549999999</v>
+        <v>5.280791879999999</v>
       </c>
       <c r="Q37">
-        <v>17.64993655</v>
+        <v>17.58079188</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1870950334296098</v>
+        <v>0.1888217534610471</v>
       </c>
       <c r="T37">
-        <v>0.985171503873019</v>
+        <v>0.9972109601005175</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.210659621341745</v>
+        <v>3.121474631860031</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1369991222150702</v>
+        <v>0.1366819727008939</v>
       </c>
       <c r="C38">
-        <v>105.8976437340558</v>
+        <v>104.5847771991867</v>
       </c>
       <c r="D38">
-        <v>65.37364373405579</v>
+        <v>65.6017771991867</v>
       </c>
       <c r="E38">
-        <v>55.476</v>
+        <v>57.017</v>
       </c>
       <c r="F38">
-        <v>55.476</v>
+        <v>57.017</v>
       </c>
       <c r="G38">
         <v>96</v>
@@ -4525,28 +4525,28 @@
         <v>11.1</v>
       </c>
       <c r="M38">
-        <v>3.5560116</v>
+        <v>3.6547897</v>
       </c>
       <c r="N38">
-        <v>7.5439884</v>
+        <v>7.445210299999999</v>
       </c>
       <c r="O38">
-        <v>2.26319652</v>
+        <v>2.23356309</v>
       </c>
       <c r="P38">
-        <v>5.280791880000001</v>
+        <v>5.21164721</v>
       </c>
       <c r="Q38">
-        <v>17.58079188</v>
+        <v>17.51164721</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1888217534610471</v>
+        <v>0.1906032900014189</v>
       </c>
       <c r="T38">
-        <v>0.9972109601005175</v>
+        <v>1.009632621287619</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.121474631860031</v>
+        <v>3.037110452620571</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1366819727008939</v>
+        <v>0.1384396231867177</v>
       </c>
       <c r="C39">
-        <v>104.5847771991867</v>
+        <v>101.7991154486456</v>
       </c>
       <c r="D39">
-        <v>65.6017771991867</v>
+        <v>64.35711544864556</v>
       </c>
       <c r="E39">
-        <v>57.017</v>
+        <v>58.558</v>
       </c>
       <c r="F39">
-        <v>57.017</v>
+        <v>58.558</v>
       </c>
       <c r="G39">
         <v>96</v>
@@ -4607,45 +4607,45 @@
         <v>11.1</v>
       </c>
       <c r="M39">
-        <v>3.6547897</v>
+        <v>4.2103202</v>
       </c>
       <c r="N39">
-        <v>7.445210299999999</v>
+        <v>6.8896798</v>
       </c>
       <c r="O39">
-        <v>2.23356309</v>
+        <v>2.06690394</v>
       </c>
       <c r="P39">
-        <v>5.21164721</v>
+        <v>4.82277586</v>
       </c>
       <c r="Q39">
-        <v>17.51164721</v>
+        <v>17.12277586</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1906032900014189</v>
+        <v>0.1924422954624478</v>
       </c>
       <c r="T39">
-        <v>1.009632621287619</v>
+        <v>1.022454981222692</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.037110452620571</v>
+        <v>2.636379057345804</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1384396231867177</v>
+        <v>0.1381770736725414</v>
       </c>
       <c r="C40">
-        <v>101.7991154486456</v>
+        <v>100.4410280342371</v>
       </c>
       <c r="D40">
-        <v>64.35711544864556</v>
+        <v>64.5400280342371</v>
       </c>
       <c r="E40">
-        <v>58.558</v>
+        <v>60.099</v>
       </c>
       <c r="F40">
-        <v>58.558</v>
+        <v>60.099</v>
       </c>
       <c r="G40">
         <v>96</v>
@@ -4689,28 +4689,28 @@
         <v>11.1</v>
       </c>
       <c r="M40">
-        <v>4.2103202</v>
+        <v>4.321118100000001</v>
       </c>
       <c r="N40">
-        <v>6.8896798</v>
+        <v>6.778881899999999</v>
       </c>
       <c r="O40">
-        <v>2.06690394</v>
+        <v>2.03366457</v>
       </c>
       <c r="P40">
-        <v>4.82277586</v>
+        <v>4.745217329999999</v>
       </c>
       <c r="Q40">
-        <v>17.12277586</v>
+        <v>17.04521733</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1924422954624478</v>
+        <v>0.1943415961844941</v>
       </c>
       <c r="T40">
-        <v>1.022454981222692</v>
+        <v>1.035697746401537</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.636379057345804</v>
+        <v>2.568779594336938</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1381770736725414</v>
+        <v>0.1379145241583652</v>
       </c>
       <c r="C41">
-        <v>100.4410280342371</v>
+        <v>99.08398331338695</v>
       </c>
       <c r="D41">
-        <v>64.5400280342371</v>
+        <v>64.72398331338697</v>
       </c>
       <c r="E41">
-        <v>60.099</v>
+        <v>61.64</v>
       </c>
       <c r="F41">
-        <v>60.099</v>
+        <v>61.64</v>
       </c>
       <c r="G41">
         <v>96</v>
@@ -4771,28 +4771,28 @@
         <v>11.1</v>
       </c>
       <c r="M41">
-        <v>4.321118100000001</v>
+        <v>4.431916</v>
       </c>
       <c r="N41">
-        <v>6.778881899999999</v>
+        <v>6.668083999999999</v>
       </c>
       <c r="O41">
-        <v>2.03366457</v>
+        <v>2.0004252</v>
       </c>
       <c r="P41">
-        <v>4.745217329999999</v>
+        <v>4.6676588</v>
       </c>
       <c r="Q41">
-        <v>17.04521733</v>
+        <v>16.9676588</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1943415961844941</v>
+        <v>0.1963042069306087</v>
       </c>
       <c r="T41">
-        <v>1.035697746401537</v>
+        <v>1.049381937086344</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.568779594336938</v>
+        <v>2.504560104478514</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1379145241583652</v>
+        <v>0.138771274644189</v>
       </c>
       <c r="C42">
-        <v>99.08398331338695</v>
+        <v>96.94653775146028</v>
       </c>
       <c r="D42">
-        <v>64.72398331338697</v>
+        <v>64.12753775146028</v>
       </c>
       <c r="E42">
-        <v>61.64</v>
+        <v>63.181</v>
       </c>
       <c r="F42">
-        <v>61.64</v>
+        <v>63.181</v>
       </c>
       <c r="G42">
         <v>96</v>
@@ -4853,45 +4853,45 @@
         <v>11.1</v>
       </c>
       <c r="M42">
-        <v>4.431916</v>
+        <v>4.789119800000001</v>
       </c>
       <c r="N42">
-        <v>6.668083999999999</v>
+        <v>6.310880199999999</v>
       </c>
       <c r="O42">
-        <v>2.0004252</v>
+        <v>1.893264059999999</v>
       </c>
       <c r="P42">
-        <v>4.6676588</v>
+        <v>4.41761614</v>
       </c>
       <c r="Q42">
-        <v>16.9676588</v>
+        <v>16.71761614</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1963042069306087</v>
+        <v>0.1983333468545575</v>
       </c>
       <c r="T42">
-        <v>1.049381937086344</v>
+        <v>1.063529998641823</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.504560104478514</v>
+        <v>2.317753671561943</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.138771274644189</v>
+        <v>0.1385360251300127</v>
       </c>
       <c r="C43">
-        <v>96.94653775146028</v>
+        <v>95.56821425263877</v>
       </c>
       <c r="D43">
-        <v>64.12753775146028</v>
+        <v>64.29021425263878</v>
       </c>
       <c r="E43">
-        <v>63.181</v>
+        <v>64.72200000000001</v>
       </c>
       <c r="F43">
-        <v>63.181</v>
+        <v>64.72200000000001</v>
       </c>
       <c r="G43">
         <v>96</v>
@@ -4935,28 +4935,28 @@
         <v>11.1</v>
       </c>
       <c r="M43">
-        <v>4.789119800000001</v>
+        <v>4.905927600000001</v>
       </c>
       <c r="N43">
-        <v>6.310880199999999</v>
+        <v>6.194072399999999</v>
       </c>
       <c r="O43">
-        <v>1.893264059999999</v>
+        <v>1.85822172</v>
       </c>
       <c r="P43">
-        <v>4.41761614</v>
+        <v>4.335850679999999</v>
       </c>
       <c r="Q43">
-        <v>16.71761614</v>
+        <v>16.63585068</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1983333468545575</v>
+        <v>0.2004324571207116</v>
       </c>
       <c r="T43">
-        <v>1.063529998641823</v>
+        <v>1.078165924388869</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.317753671561943</v>
+        <v>2.262569060334278</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1385360251300127</v>
+        <v>0.1383007756158365</v>
       </c>
       <c r="C44">
-        <v>95.56821425263881</v>
+        <v>94.19071819699523</v>
       </c>
       <c r="D44">
-        <v>64.29021425263879</v>
+        <v>64.45371819699523</v>
       </c>
       <c r="E44">
-        <v>64.72199999999999</v>
+        <v>66.26299999999999</v>
       </c>
       <c r="F44">
-        <v>64.72199999999999</v>
+        <v>66.26299999999999</v>
       </c>
       <c r="G44">
         <v>96</v>
@@ -5017,28 +5017,28 @@
         <v>11.1</v>
       </c>
       <c r="M44">
-        <v>4.9059276</v>
+        <v>5.022735399999999</v>
       </c>
       <c r="N44">
-        <v>6.1940724</v>
+        <v>6.0772646</v>
       </c>
       <c r="O44">
-        <v>1.85822172</v>
+        <v>1.82317938</v>
       </c>
       <c r="P44">
-        <v>4.33585068</v>
+        <v>4.25408522</v>
       </c>
       <c r="Q44">
-        <v>16.63585068</v>
+        <v>16.55408522</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2004324571207115</v>
+        <v>0.2026052203786604</v>
       </c>
       <c r="T44">
-        <v>1.078165924388869</v>
+        <v>1.093315391390198</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.262569060334278</v>
+        <v>2.209951175210225</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1383007756158365</v>
+        <v>0.1380655261016602</v>
       </c>
       <c r="C45">
-        <v>94.19071819699523</v>
+        <v>92.81405591372803</v>
       </c>
       <c r="D45">
-        <v>64.45371819699523</v>
+        <v>64.61805591372801</v>
       </c>
       <c r="E45">
-        <v>66.26299999999999</v>
+        <v>67.804</v>
       </c>
       <c r="F45">
-        <v>66.26299999999999</v>
+        <v>67.804</v>
       </c>
       <c r="G45">
         <v>96</v>
@@ -5099,28 +5099,28 @@
         <v>11.1</v>
       </c>
       <c r="M45">
-        <v>5.022735399999999</v>
+        <v>5.1395432</v>
       </c>
       <c r="N45">
-        <v>6.0772646</v>
+        <v>5.960456799999999</v>
       </c>
       <c r="O45">
-        <v>1.82317938</v>
+        <v>1.78813704</v>
       </c>
       <c r="P45">
-        <v>4.25408522</v>
+        <v>4.17231976</v>
       </c>
       <c r="Q45">
-        <v>16.55408522</v>
+        <v>16.47231976</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2026052203786604</v>
+        <v>0.2048555823243932</v>
       </c>
       <c r="T45">
-        <v>1.093315391390198</v>
+        <v>1.109005910784432</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.209951175210225</v>
+        <v>2.159725012137265</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1380655261016602</v>
+        <v>0.137830276587484</v>
       </c>
       <c r="C46">
-        <v>92.81405591372803</v>
+        <v>91.43823379675072</v>
       </c>
       <c r="D46">
-        <v>64.61805591372801</v>
+        <v>64.78323379675072</v>
       </c>
       <c r="E46">
-        <v>67.804</v>
+        <v>69.345</v>
       </c>
       <c r="F46">
-        <v>67.804</v>
+        <v>69.345</v>
       </c>
       <c r="G46">
         <v>96</v>
@@ -5181,28 +5181,28 @@
         <v>11.1</v>
       </c>
       <c r="M46">
-        <v>5.1395432</v>
+        <v>5.256351</v>
       </c>
       <c r="N46">
-        <v>5.960456799999999</v>
+        <v>5.843648999999999</v>
       </c>
       <c r="O46">
-        <v>1.78813704</v>
+        <v>1.7530947</v>
       </c>
       <c r="P46">
-        <v>4.17231976</v>
+        <v>4.090554299999999</v>
       </c>
       <c r="Q46">
-        <v>16.47231976</v>
+        <v>16.3905543</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2048555823243932</v>
+        <v>0.2071877756136072</v>
       </c>
       <c r="T46">
-        <v>1.109005910784432</v>
+        <v>1.125266994520274</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.159725012137265</v>
+        <v>2.111731122978659</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.137830276587484</v>
+        <v>0.1375950270733077</v>
       </c>
       <c r="C47">
-        <v>91.43823379675072</v>
+        <v>90.06325830552157</v>
       </c>
       <c r="D47">
-        <v>64.78323379675072</v>
+        <v>64.94925830552157</v>
       </c>
       <c r="E47">
-        <v>69.345</v>
+        <v>70.886</v>
       </c>
       <c r="F47">
-        <v>69.345</v>
+        <v>70.886</v>
       </c>
       <c r="G47">
         <v>96</v>
@@ -5263,28 +5263,28 @@
         <v>11.1</v>
       </c>
       <c r="M47">
-        <v>5.256351</v>
+        <v>5.3731588</v>
       </c>
       <c r="N47">
-        <v>5.843648999999999</v>
+        <v>5.7268412</v>
       </c>
       <c r="O47">
-        <v>1.7530947</v>
+        <v>1.71805236</v>
       </c>
       <c r="P47">
-        <v>4.090554299999999</v>
+        <v>4.00878884</v>
       </c>
       <c r="Q47">
-        <v>16.3905543</v>
+        <v>16.30878884</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2071877756136072</v>
+        <v>0.2096063464320513</v>
       </c>
       <c r="T47">
-        <v>1.125266994520274</v>
+        <v>1.142130340616703</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.111731122978659</v>
+        <v>2.065823924653037</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1375950270733077</v>
+        <v>0.1373597775591315</v>
       </c>
       <c r="C48">
-        <v>90.06325830552157</v>
+        <v>88.6891359658852</v>
       </c>
       <c r="D48">
-        <v>64.94925830552157</v>
+        <v>65.11613596588521</v>
       </c>
       <c r="E48">
-        <v>70.886</v>
+        <v>72.42700000000001</v>
       </c>
       <c r="F48">
-        <v>70.886</v>
+        <v>72.42700000000001</v>
       </c>
       <c r="G48">
         <v>96</v>
@@ -5345,28 +5345,28 @@
         <v>11.1</v>
       </c>
       <c r="M48">
-        <v>5.3731588</v>
+        <v>5.489966600000001</v>
       </c>
       <c r="N48">
-        <v>5.7268412</v>
+        <v>5.610033399999999</v>
       </c>
       <c r="O48">
-        <v>1.71805236</v>
+        <v>1.68301002</v>
       </c>
       <c r="P48">
-        <v>4.00878884</v>
+        <v>3.92702338</v>
       </c>
       <c r="Q48">
-        <v>16.30878884</v>
+        <v>16.22702338</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2096063464320513</v>
+        <v>0.212116184073833</v>
       </c>
       <c r="T48">
-        <v>1.142130340616703</v>
+        <v>1.159630039396016</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.065823924653037</v>
+        <v>2.021870224128504</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1373597775591315</v>
+        <v>0.1418957280449552</v>
       </c>
       <c r="C49">
-        <v>88.6891359658852</v>
+        <v>84.0744970583237</v>
       </c>
       <c r="D49">
-        <v>65.11613596588521</v>
+        <v>62.0424970583237</v>
       </c>
       <c r="E49">
-        <v>72.42700000000001</v>
+        <v>73.968</v>
       </c>
       <c r="F49">
-        <v>72.42700000000001</v>
+        <v>73.968</v>
       </c>
       <c r="G49">
         <v>96</v>
@@ -5427,45 +5427,45 @@
         <v>11.1</v>
       </c>
       <c r="M49">
-        <v>5.489966600000001</v>
+        <v>6.65712</v>
       </c>
       <c r="N49">
-        <v>5.610033399999999</v>
+        <v>4.44288</v>
       </c>
       <c r="O49">
-        <v>1.68301002</v>
+        <v>1.332864</v>
       </c>
       <c r="P49">
-        <v>3.92702338</v>
+        <v>3.110016</v>
       </c>
       <c r="Q49">
-        <v>16.22702338</v>
+        <v>15.410016</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.212116184073833</v>
+        <v>0.2147225539326062</v>
       </c>
       <c r="T49">
-        <v>1.159630039396016</v>
+        <v>1.177802803512995</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.021870224128504</v>
+        <v>1.667387699185233</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1418957280449552</v>
+        <v>0.141759878530779</v>
       </c>
       <c r="C50">
-        <v>84.07449705832371</v>
+        <v>82.62133004865991</v>
       </c>
       <c r="D50">
-        <v>62.0424970583237</v>
+        <v>62.1303300486599</v>
       </c>
       <c r="E50">
-        <v>73.96799999999999</v>
+        <v>75.509</v>
       </c>
       <c r="F50">
-        <v>73.96799999999999</v>
+        <v>75.509</v>
       </c>
       <c r="G50">
         <v>96</v>
@@ -5509,28 +5509,28 @@
         <v>11.1</v>
       </c>
       <c r="M50">
-        <v>6.657119999999999</v>
+        <v>6.795809999999999</v>
       </c>
       <c r="N50">
-        <v>4.442880000000001</v>
+        <v>4.30419</v>
       </c>
       <c r="O50">
-        <v>1.332864</v>
+        <v>1.291257</v>
       </c>
       <c r="P50">
-        <v>3.110016000000001</v>
+        <v>3.012933</v>
       </c>
       <c r="Q50">
-        <v>15.410016</v>
+        <v>15.312933</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2147225539326062</v>
+        <v>0.2174311343740764</v>
       </c>
       <c r="T50">
-        <v>1.177802803512995</v>
+        <v>1.196688225046326</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.667387699185233</v>
+        <v>1.633359378793698</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.141759878530779</v>
+        <v>0.1416240290166027</v>
       </c>
       <c r="C51">
-        <v>82.62133004865991</v>
+        <v>81.16841208026865</v>
       </c>
       <c r="D51">
-        <v>62.1303300486599</v>
+        <v>62.21841208026866</v>
       </c>
       <c r="E51">
-        <v>75.509</v>
+        <v>77.05</v>
       </c>
       <c r="F51">
-        <v>75.509</v>
+        <v>77.05</v>
       </c>
       <c r="G51">
         <v>96</v>
@@ -5591,28 +5591,28 @@
         <v>11.1</v>
       </c>
       <c r="M51">
-        <v>6.795809999999999</v>
+        <v>6.9345</v>
       </c>
       <c r="N51">
-        <v>4.30419</v>
+        <v>4.1655</v>
       </c>
       <c r="O51">
-        <v>1.291257</v>
+        <v>1.24965</v>
       </c>
       <c r="P51">
-        <v>3.012933</v>
+        <v>2.91585</v>
       </c>
       <c r="Q51">
-        <v>15.312933</v>
+        <v>15.21585</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2174311343740764</v>
+        <v>0.2202480580332055</v>
       </c>
       <c r="T51">
-        <v>1.196688225046326</v>
+        <v>1.21632906344099</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.633359378793698</v>
+        <v>1.600692191217824</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1416240290166027</v>
+        <v>0.1414881795024265</v>
       </c>
       <c r="C52">
-        <v>81.16841208026865</v>
+        <v>79.71574421384959</v>
       </c>
       <c r="D52">
-        <v>62.21841208026866</v>
+        <v>62.30674421384957</v>
       </c>
       <c r="E52">
-        <v>77.05</v>
+        <v>78.59099999999999</v>
       </c>
       <c r="F52">
-        <v>77.05</v>
+        <v>78.59099999999999</v>
       </c>
       <c r="G52">
         <v>96</v>
@@ -5673,28 +5673,28 @@
         <v>11.1</v>
       </c>
       <c r="M52">
-        <v>6.9345</v>
+        <v>7.073189999999999</v>
       </c>
       <c r="N52">
-        <v>4.1655</v>
+        <v>4.02681</v>
       </c>
       <c r="O52">
-        <v>1.24965</v>
+        <v>1.208043</v>
       </c>
       <c r="P52">
-        <v>2.91585</v>
+        <v>2.818767</v>
       </c>
       <c r="Q52">
-        <v>15.21585</v>
+        <v>15.118767</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2202480580332055</v>
+        <v>0.2231799581682173</v>
       </c>
       <c r="T52">
-        <v>1.21632906344099</v>
+        <v>1.236771568708906</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.600692191217824</v>
+        <v>1.569306069821396</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1414881795024265</v>
+        <v>0.1413523299882502</v>
       </c>
       <c r="C53">
-        <v>79.71574421384959</v>
+        <v>78.26332751613424</v>
       </c>
       <c r="D53">
-        <v>62.30674421384957</v>
+        <v>62.39532751613425</v>
       </c>
       <c r="E53">
-        <v>78.59099999999999</v>
+        <v>80.13200000000001</v>
       </c>
       <c r="F53">
-        <v>78.59099999999999</v>
+        <v>80.13200000000001</v>
       </c>
       <c r="G53">
         <v>96</v>
@@ -5755,28 +5755,28 @@
         <v>11.1</v>
       </c>
       <c r="M53">
-        <v>7.073189999999999</v>
+        <v>7.21188</v>
       </c>
       <c r="N53">
-        <v>4.02681</v>
+        <v>3.88812</v>
       </c>
       <c r="O53">
-        <v>1.208043</v>
+        <v>1.166436</v>
       </c>
       <c r="P53">
-        <v>2.818767</v>
+        <v>2.721684</v>
       </c>
       <c r="Q53">
-        <v>15.118767</v>
+        <v>15.021684</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2231799581682173</v>
+        <v>0.2262340208088547</v>
       </c>
       <c r="T53">
-        <v>1.236771568708906</v>
+        <v>1.258065845029651</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.569306069821396</v>
+        <v>1.539127106940215</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1413523299882502</v>
+        <v>0.141216480474074</v>
       </c>
       <c r="C54">
-        <v>78.26332751613424</v>
+        <v>76.81116305992941</v>
       </c>
       <c r="D54">
-        <v>62.39532751613425</v>
+        <v>62.48416305992942</v>
       </c>
       <c r="E54">
-        <v>80.13200000000001</v>
+        <v>81.673</v>
       </c>
       <c r="F54">
-        <v>80.13200000000001</v>
+        <v>81.673</v>
       </c>
       <c r="G54">
         <v>96</v>
@@ -5837,28 +5837,28 @@
         <v>11.1</v>
       </c>
       <c r="M54">
-        <v>7.21188</v>
+        <v>7.35057</v>
       </c>
       <c r="N54">
-        <v>3.88812</v>
+        <v>3.749429999999999</v>
       </c>
       <c r="O54">
-        <v>1.166436</v>
+        <v>1.124829</v>
       </c>
       <c r="P54">
-        <v>2.721684</v>
+        <v>2.624600999999999</v>
       </c>
       <c r="Q54">
-        <v>15.021684</v>
+        <v>14.924601</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2262340208088547</v>
+        <v>0.2294180435618596</v>
       </c>
       <c r="T54">
-        <v>1.258065845029651</v>
+        <v>1.280266260768301</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.539127106940215</v>
+        <v>1.510086972847004</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.141216480474074</v>
+        <v>0.1662417418173087</v>
       </c>
       <c r="C55">
-        <v>76.81116305992941</v>
+        <v>62.28726787098498</v>
       </c>
       <c r="D55">
-        <v>62.48416305992942</v>
+        <v>49.50126787098498</v>
       </c>
       <c r="E55">
-        <v>81.673</v>
+        <v>83.214</v>
       </c>
       <c r="F55">
-        <v>81.673</v>
+        <v>83.214</v>
       </c>
       <c r="G55">
         <v>96</v>
@@ -5919,45 +5919,45 @@
         <v>11.1</v>
       </c>
       <c r="M55">
-        <v>7.35057</v>
+        <v>12.2158152</v>
       </c>
       <c r="N55">
-        <v>3.749429999999999</v>
+        <v>-1.115815200000002</v>
       </c>
       <c r="O55">
-        <v>1.124829</v>
+        <v>-0.3347445600000006</v>
       </c>
       <c r="P55">
-        <v>2.624600999999999</v>
+        <v>-0.7810706400000014</v>
       </c>
       <c r="Q55">
-        <v>14.924601</v>
+        <v>11.51892936</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2294180435618596</v>
+        <v>0.2360414921711941</v>
       </c>
       <c r="T55">
-        <v>1.280266260768301</v>
+        <v>1.326447875711862</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.3</v>
+        <v>0.272597444008485</v>
       </c>
       <c r="W55">
-        <v>0.063</v>
+        <v>0.1067826952195544</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.510086972847004</v>
+        <v>0.9086581466949498</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1662417418173087</v>
+        <v>0.1672517418173087</v>
       </c>
       <c r="C56">
-        <v>62.28726787098498</v>
+        <v>60.33461234590486</v>
       </c>
       <c r="D56">
-        <v>49.50126787098498</v>
+        <v>49.08961234590488</v>
       </c>
       <c r="E56">
-        <v>83.214</v>
+        <v>84.75500000000001</v>
       </c>
       <c r="F56">
-        <v>83.214</v>
+        <v>84.75500000000001</v>
       </c>
       <c r="G56">
         <v>96</v>
@@ -6001,37 +6001,37 @@
         <v>11.1</v>
       </c>
       <c r="M56">
-        <v>12.2158152</v>
+        <v>12.442034</v>
       </c>
       <c r="N56">
-        <v>-1.115815200000002</v>
+        <v>-1.342034000000004</v>
       </c>
       <c r="O56">
-        <v>-0.3347445600000006</v>
+        <v>-0.402610200000001</v>
       </c>
       <c r="P56">
-        <v>-0.7810706400000014</v>
+        <v>-0.9394238000000025</v>
       </c>
       <c r="Q56">
-        <v>11.51892936</v>
+        <v>11.3605762</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2360414921711941</v>
+        <v>0.2402690808861096</v>
       </c>
       <c r="T56">
-        <v>1.326447875711862</v>
+        <v>1.355924495172126</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.272597444008485</v>
+        <v>0.2676411268446943</v>
       </c>
       <c r="W56">
-        <v>0.1067826952195544</v>
+        <v>0.1075102825791989</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9086581466949498</v>
+        <v>0.8921370894823143</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1672517418173087</v>
+        <v>0.1682617418173087</v>
       </c>
       <c r="C57">
-        <v>60.33461234590486</v>
+        <v>58.38874705709226</v>
       </c>
       <c r="D57">
-        <v>49.08961234590488</v>
+        <v>48.68474705709226</v>
       </c>
       <c r="E57">
-        <v>84.75500000000001</v>
+        <v>86.29600000000001</v>
       </c>
       <c r="F57">
-        <v>84.75500000000001</v>
+        <v>86.29600000000001</v>
       </c>
       <c r="G57">
         <v>96</v>
@@ -6083,37 +6083,37 @@
         <v>11.1</v>
       </c>
       <c r="M57">
-        <v>12.442034</v>
+        <v>12.6682528</v>
       </c>
       <c r="N57">
-        <v>-1.342034000000004</v>
+        <v>-1.568252800000003</v>
       </c>
       <c r="O57">
-        <v>-0.402610200000001</v>
+        <v>-0.470475840000001</v>
       </c>
       <c r="P57">
-        <v>-0.9394238000000025</v>
+        <v>-1.097776960000002</v>
       </c>
       <c r="Q57">
-        <v>11.3605762</v>
+        <v>11.20222304</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2402690808861096</v>
+        <v>0.2446888327244302</v>
       </c>
       <c r="T57">
-        <v>1.355924495172126</v>
+        <v>1.386740960971492</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2676411268446943</v>
+        <v>0.2628618210081819</v>
       </c>
       <c r="W57">
-        <v>0.1075102825791989</v>
+        <v>0.1082118846759989</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8921370894823143</v>
+        <v>0.876206070027273</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1682617418173087</v>
+        <v>0.1692717418173087</v>
       </c>
       <c r="C58">
-        <v>58.38874705709226</v>
+        <v>56.44950537195898</v>
       </c>
       <c r="D58">
-        <v>48.68474705709226</v>
+        <v>48.28650537195899</v>
       </c>
       <c r="E58">
-        <v>86.29600000000001</v>
+        <v>87.837</v>
       </c>
       <c r="F58">
-        <v>86.29600000000001</v>
+        <v>87.837</v>
       </c>
       <c r="G58">
         <v>96</v>
@@ -6165,37 +6165,37 @@
         <v>11.1</v>
       </c>
       <c r="M58">
-        <v>12.6682528</v>
+        <v>12.8944716</v>
       </c>
       <c r="N58">
-        <v>-1.568252800000003</v>
+        <v>-1.794471600000001</v>
       </c>
       <c r="O58">
-        <v>-0.470475840000001</v>
+        <v>-0.5383414800000004</v>
       </c>
       <c r="P58">
-        <v>-1.097776960000002</v>
+        <v>-1.256130120000001</v>
       </c>
       <c r="Q58">
-        <v>11.20222304</v>
+        <v>11.04386988</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2446888327244302</v>
+        <v>0.2493141544156961</v>
       </c>
       <c r="T58">
-        <v>1.386740960971492</v>
+        <v>1.418990750761527</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2628618210081819</v>
+        <v>0.2582502101133016</v>
       </c>
       <c r="W58">
-        <v>0.1082118846759989</v>
+        <v>0.1088888691553673</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.876206070027273</v>
+        <v>0.8608340337110052</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1692717418173087</v>
+        <v>0.1702817418173087</v>
       </c>
       <c r="C59">
-        <v>56.44950537195898</v>
+        <v>54.51672606590418</v>
       </c>
       <c r="D59">
-        <v>48.28650537195899</v>
+        <v>47.89472606590419</v>
       </c>
       <c r="E59">
-        <v>87.837</v>
+        <v>89.37800000000001</v>
       </c>
       <c r="F59">
-        <v>87.837</v>
+        <v>89.37800000000001</v>
       </c>
       <c r="G59">
         <v>96</v>
@@ -6247,37 +6247,37 @@
         <v>11.1</v>
       </c>
       <c r="M59">
-        <v>12.8944716</v>
+        <v>13.1206904</v>
       </c>
       <c r="N59">
-        <v>-1.794471600000001</v>
+        <v>-2.020690400000003</v>
       </c>
       <c r="O59">
-        <v>-0.5383414800000004</v>
+        <v>-0.6062071200000009</v>
       </c>
       <c r="P59">
-        <v>-1.256130120000001</v>
+        <v>-1.414483280000002</v>
       </c>
       <c r="Q59">
-        <v>11.04386988</v>
+        <v>10.88551672</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2493141544156961</v>
+        <v>0.2541597295208317</v>
       </c>
       <c r="T59">
-        <v>1.418990750761527</v>
+        <v>1.452776244827278</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2582502101133016</v>
+        <v>0.2537976202837618</v>
       </c>
       <c r="W59">
-        <v>0.1088888691553673</v>
+        <v>0.1095425093423438</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8608340337110052</v>
+        <v>0.8459920676125394</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1702817418173087</v>
+        <v>0.1712917418173087</v>
       </c>
       <c r="C60">
-        <v>54.51672606590421</v>
+        <v>52.59025310468748</v>
       </c>
       <c r="D60">
-        <v>47.89472606590419</v>
+        <v>47.50925310468747</v>
       </c>
       <c r="E60">
-        <v>89.37799999999999</v>
+        <v>90.919</v>
       </c>
       <c r="F60">
-        <v>89.37799999999999</v>
+        <v>90.919</v>
       </c>
       <c r="G60">
         <v>96</v>
@@ -6329,37 +6329,37 @@
         <v>11.1</v>
       </c>
       <c r="M60">
-        <v>13.1206904</v>
+        <v>13.3469092</v>
       </c>
       <c r="N60">
-        <v>-2.020690399999999</v>
+        <v>-2.246909200000001</v>
       </c>
       <c r="O60">
-        <v>-0.6062071199999998</v>
+        <v>-0.6740727600000003</v>
       </c>
       <c r="P60">
-        <v>-1.41448328</v>
+        <v>-1.572836440000001</v>
       </c>
       <c r="Q60">
-        <v>10.88551672</v>
+        <v>10.72716356</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2541597295208317</v>
+        <v>0.2592416741432909</v>
       </c>
       <c r="T60">
-        <v>1.452776244827277</v>
+        <v>1.488209811774284</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2537976202837619</v>
+        <v>0.2494959657026811</v>
       </c>
       <c r="W60">
-        <v>0.1095425093423438</v>
+        <v>0.1101739922348464</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8459920676125396</v>
+        <v>0.8316532190089372</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1712917418173087</v>
+        <v>0.1723017418173087</v>
       </c>
       <c r="C61">
-        <v>52.59025310468748</v>
+        <v>50.66993543722775</v>
       </c>
       <c r="D61">
-        <v>47.50925310468747</v>
+        <v>47.12993543722773</v>
       </c>
       <c r="E61">
-        <v>90.919</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="F61">
-        <v>90.919</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="G61">
         <v>96</v>
@@ -6411,37 +6411,37 @@
         <v>11.1</v>
       </c>
       <c r="M61">
-        <v>13.3469092</v>
+        <v>13.573128</v>
       </c>
       <c r="N61">
-        <v>-2.246909200000001</v>
+        <v>-2.473128000000001</v>
       </c>
       <c r="O61">
-        <v>-0.6740727600000003</v>
+        <v>-0.7419384000000002</v>
       </c>
       <c r="P61">
-        <v>-1.572836440000001</v>
+        <v>-1.731189600000001</v>
       </c>
       <c r="Q61">
-        <v>10.72716356</v>
+        <v>10.5688104</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2592416741432909</v>
+        <v>0.2645777159968732</v>
       </c>
       <c r="T61">
-        <v>1.488209811774284</v>
+        <v>1.525415057068641</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2494959657026811</v>
+        <v>0.2453376996076365</v>
       </c>
       <c r="W61">
-        <v>0.1101739922348464</v>
+        <v>0.110784425697599</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8316532190089372</v>
+        <v>0.817792332025455</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1723017418173087</v>
+        <v>0.1733117418173087</v>
       </c>
       <c r="C62">
-        <v>50.66993543722775</v>
+        <v>48.75562679824922</v>
       </c>
       <c r="D62">
-        <v>47.12993543722773</v>
+        <v>46.75662679824921</v>
       </c>
       <c r="E62">
-        <v>92.45999999999999</v>
+        <v>94.00099999999999</v>
       </c>
       <c r="F62">
-        <v>92.45999999999999</v>
+        <v>94.00099999999999</v>
       </c>
       <c r="G62">
         <v>96</v>
@@ -6493,37 +6493,37 @@
         <v>11.1</v>
       </c>
       <c r="M62">
-        <v>13.573128</v>
+        <v>13.7993468</v>
       </c>
       <c r="N62">
-        <v>-2.473128000000001</v>
+        <v>-2.699346800000001</v>
       </c>
       <c r="O62">
-        <v>-0.7419384000000002</v>
+        <v>-0.8098040400000002</v>
       </c>
       <c r="P62">
-        <v>-1.731189600000001</v>
+        <v>-1.889542760000001</v>
       </c>
       <c r="Q62">
-        <v>10.5688104</v>
+        <v>10.41045724</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2645777159968732</v>
+        <v>0.2701874010224341</v>
       </c>
       <c r="T62">
-        <v>1.525415057068641</v>
+        <v>1.564528263660145</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2453376996076365</v>
+        <v>0.2413157701058719</v>
       </c>
       <c r="W62">
-        <v>0.110784425697599</v>
+        <v>0.111374844948458</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.817792332025455</v>
+        <v>0.8043859003529066</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1733117418173087</v>
+        <v>0.2118639559091411</v>
       </c>
       <c r="C63">
-        <v>48.75562679824922</v>
+        <v>36.35994447619098</v>
       </c>
       <c r="D63">
-        <v>46.75662679824921</v>
+        <v>35.90194447619098</v>
       </c>
       <c r="E63">
-        <v>94.00099999999999</v>
+        <v>95.542</v>
       </c>
       <c r="F63">
-        <v>94.00099999999999</v>
+        <v>95.542</v>
       </c>
       <c r="G63">
         <v>96</v>
@@ -6575,45 +6575,45 @@
         <v>11.1</v>
       </c>
       <c r="M63">
-        <v>13.7993468</v>
+        <v>19.1848336</v>
       </c>
       <c r="N63">
-        <v>-2.699346800000001</v>
+        <v>-8.084833600000001</v>
       </c>
       <c r="O63">
-        <v>-0.8098040400000002</v>
+        <v>-2.425450080000001</v>
       </c>
       <c r="P63">
-        <v>-1.889542760000001</v>
+        <v>-5.65938352</v>
       </c>
       <c r="Q63">
-        <v>10.41045724</v>
+        <v>6.640616479999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2701874010224341</v>
+        <v>0.2867823697120571</v>
       </c>
       <c r="T63">
-        <v>1.564528263660145</v>
+        <v>1.680235729548011</v>
       </c>
       <c r="U63">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.2413157701058719</v>
+        <v>0.173574609476936</v>
       </c>
       <c r="W63">
-        <v>0.111374844948458</v>
+        <v>0.1659462184170313</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8043859003529066</v>
+        <v>0.5785820315897866</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2118639559091411</v>
+        <v>0.2134139559091411</v>
       </c>
       <c r="C64">
-        <v>36.35994447619098</v>
+        <v>34.48694339885671</v>
       </c>
       <c r="D64">
-        <v>35.90194447619098</v>
+        <v>35.56994339885669</v>
       </c>
       <c r="E64">
-        <v>95.542</v>
+        <v>97.083</v>
       </c>
       <c r="F64">
-        <v>95.542</v>
+        <v>97.083</v>
       </c>
       <c r="G64">
         <v>96</v>
@@ -6657,37 +6657,37 @@
         <v>11.1</v>
       </c>
       <c r="M64">
-        <v>19.1848336</v>
+        <v>19.4942664</v>
       </c>
       <c r="N64">
-        <v>-8.084833600000001</v>
+        <v>-8.394266400000001</v>
       </c>
       <c r="O64">
-        <v>-2.425450080000001</v>
+        <v>-2.51827992</v>
       </c>
       <c r="P64">
-        <v>-5.65938352</v>
+        <v>-5.875986480000001</v>
       </c>
       <c r="Q64">
-        <v>6.640616479999998</v>
+        <v>6.424013519999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2867823697120571</v>
+        <v>0.2932954067313018</v>
       </c>
       <c r="T64">
-        <v>1.680235729548011</v>
+        <v>1.725647506022282</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.173574609476936</v>
+        <v>0.170819456945556</v>
       </c>
       <c r="W64">
-        <v>0.1659462184170313</v>
+        <v>0.1664994530453324</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5785820315897866</v>
+        <v>0.5693981898185201</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2134139559091411</v>
+        <v>0.2149639559091411</v>
       </c>
       <c r="C65">
-        <v>34.48694339885671</v>
+        <v>32.62002637964346</v>
       </c>
       <c r="D65">
-        <v>35.56994339885669</v>
+        <v>35.24402637964345</v>
       </c>
       <c r="E65">
-        <v>97.083</v>
+        <v>98.624</v>
       </c>
       <c r="F65">
-        <v>97.083</v>
+        <v>98.624</v>
       </c>
       <c r="G65">
         <v>96</v>
@@ -6739,37 +6739,37 @@
         <v>11.1</v>
       </c>
       <c r="M65">
-        <v>19.4942664</v>
+        <v>19.8036992</v>
       </c>
       <c r="N65">
-        <v>-8.394266400000001</v>
+        <v>-8.703699200000001</v>
       </c>
       <c r="O65">
-        <v>-2.51827992</v>
+        <v>-2.61110976</v>
       </c>
       <c r="P65">
-        <v>-5.875986480000001</v>
+        <v>-6.092589440000001</v>
       </c>
       <c r="Q65">
-        <v>6.424013519999998</v>
+        <v>6.207410559999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2932954067313018</v>
+        <v>0.3001702791405047</v>
       </c>
       <c r="T65">
-        <v>1.725647506022282</v>
+        <v>1.773582158967345</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.170819456945556</v>
+        <v>0.1681504029307817</v>
       </c>
       <c r="W65">
-        <v>0.1664994530453324</v>
+        <v>0.167035399091499</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5693981898185201</v>
+        <v>0.5605013431026058</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2149639559091411</v>
+        <v>0.2165139559091411</v>
       </c>
       <c r="C66">
-        <v>32.62002637964346</v>
+        <v>30.75902769765214</v>
       </c>
       <c r="D66">
-        <v>35.24402637964345</v>
+        <v>34.92402769765214</v>
       </c>
       <c r="E66">
-        <v>98.624</v>
+        <v>100.165</v>
       </c>
       <c r="F66">
-        <v>98.624</v>
+        <v>100.165</v>
       </c>
       <c r="G66">
         <v>96</v>
@@ -6821,37 +6821,37 @@
         <v>11.1</v>
       </c>
       <c r="M66">
-        <v>19.8036992</v>
+        <v>20.113132</v>
       </c>
       <c r="N66">
-        <v>-8.703699200000001</v>
+        <v>-9.013132000000001</v>
       </c>
       <c r="O66">
-        <v>-2.61110976</v>
+        <v>-2.7039396</v>
       </c>
       <c r="P66">
-        <v>-6.092589440000001</v>
+        <v>-6.309192400000001</v>
       </c>
       <c r="Q66">
-        <v>6.207410559999998</v>
+        <v>5.990807599999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3001702791405047</v>
+        <v>0.307438001401662</v>
       </c>
       <c r="T66">
-        <v>1.773582158967345</v>
+        <v>1.824255934937841</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1681504029307817</v>
+        <v>0.1655634736549235</v>
       </c>
       <c r="W66">
-        <v>0.167035399091499</v>
+        <v>0.1675548544900914</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5605013431026058</v>
+        <v>0.5518782455164118</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2165139559091411</v>
+        <v>0.2180639559091411</v>
       </c>
       <c r="C67">
-        <v>30.75902769765214</v>
+        <v>28.90378759649069</v>
       </c>
       <c r="D67">
-        <v>34.92402769765214</v>
+        <v>34.60978759649069</v>
       </c>
       <c r="E67">
-        <v>100.165</v>
+        <v>101.706</v>
       </c>
       <c r="F67">
-        <v>100.165</v>
+        <v>101.706</v>
       </c>
       <c r="G67">
         <v>96</v>
@@ -6903,37 +6903,37 @@
         <v>11.1</v>
       </c>
       <c r="M67">
-        <v>20.113132</v>
+        <v>20.4225648</v>
       </c>
       <c r="N67">
-        <v>-9.013132000000001</v>
+        <v>-9.3225648</v>
       </c>
       <c r="O67">
-        <v>-2.7039396</v>
+        <v>-2.79676944</v>
       </c>
       <c r="P67">
-        <v>-6.309192400000001</v>
+        <v>-6.52579536</v>
       </c>
       <c r="Q67">
-        <v>5.990807599999998</v>
+        <v>5.774204639999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.307438001401662</v>
+        <v>0.315133236737005</v>
       </c>
       <c r="T67">
-        <v>1.824255934937841</v>
+        <v>1.877910521259542</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1655634736549235</v>
+        <v>0.1630549361753035</v>
       </c>
       <c r="W67">
-        <v>0.1675548544900914</v>
+        <v>0.1680585688159991</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5518782455164118</v>
+        <v>0.5435164539176783</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2180639559091411</v>
+        <v>0.2196139559091411</v>
       </c>
       <c r="C68">
-        <v>28.90378759649069</v>
+        <v>27.05415201832916</v>
       </c>
       <c r="D68">
-        <v>34.60978759649069</v>
+        <v>34.30115201832916</v>
       </c>
       <c r="E68">
-        <v>101.706</v>
+        <v>103.247</v>
       </c>
       <c r="F68">
-        <v>101.706</v>
+        <v>103.247</v>
       </c>
       <c r="G68">
         <v>96</v>
@@ -6985,37 +6985,37 @@
         <v>11.1</v>
       </c>
       <c r="M68">
-        <v>20.4225648</v>
+        <v>20.7319976</v>
       </c>
       <c r="N68">
-        <v>-9.3225648</v>
+        <v>-9.6319976</v>
       </c>
       <c r="O68">
-        <v>-2.79676944</v>
+        <v>-2.88959928</v>
       </c>
       <c r="P68">
-        <v>-6.52579536</v>
+        <v>-6.74239832</v>
       </c>
       <c r="Q68">
-        <v>5.774204639999999</v>
+        <v>5.557601679999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.315133236737005</v>
+        <v>0.3232948499714597</v>
       </c>
       <c r="T68">
-        <v>1.877910521259542</v>
+        <v>1.93481690069165</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1630549361753035</v>
+        <v>0.160621280411493</v>
       </c>
       <c r="W68">
-        <v>0.1680585688159991</v>
+        <v>0.1685472468933722</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5435164539176783</v>
+        <v>0.53540426803831</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2196139559091411</v>
+        <v>0.2211639559091411</v>
       </c>
       <c r="C69">
-        <v>27.05415201832916</v>
+        <v>25.20997235205864</v>
       </c>
       <c r="D69">
-        <v>34.30115201832916</v>
+        <v>33.99797235205865</v>
       </c>
       <c r="E69">
-        <v>103.247</v>
+        <v>104.788</v>
       </c>
       <c r="F69">
-        <v>103.247</v>
+        <v>104.788</v>
       </c>
       <c r="G69">
         <v>96</v>
@@ -7067,37 +7067,37 @@
         <v>11.1</v>
       </c>
       <c r="M69">
-        <v>20.7319976</v>
+        <v>21.0414304</v>
       </c>
       <c r="N69">
-        <v>-9.6319976</v>
+        <v>-9.9414304</v>
       </c>
       <c r="O69">
-        <v>-2.88959928</v>
+        <v>-2.98242912</v>
       </c>
       <c r="P69">
-        <v>-6.74239832</v>
+        <v>-6.95900128</v>
       </c>
       <c r="Q69">
-        <v>5.557601679999999</v>
+        <v>5.340998719999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3232948499714597</v>
+        <v>0.3319665640330678</v>
       </c>
       <c r="T69">
-        <v>1.93481690069165</v>
+        <v>1.995279928838264</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.160621280411493</v>
+        <v>0.1582592027583828</v>
       </c>
       <c r="W69">
-        <v>0.1685472468933722</v>
+        <v>0.1690215520861167</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.53540426803831</v>
+        <v>0.5275306758612761</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2211639559091411</v>
+        <v>0.2227139559091411</v>
       </c>
       <c r="C70">
-        <v>25.20997235205864</v>
+        <v>23.37110519468888</v>
       </c>
       <c r="D70">
-        <v>33.99797235205865</v>
+        <v>33.7001051946889</v>
       </c>
       <c r="E70">
-        <v>104.788</v>
+        <v>106.329</v>
       </c>
       <c r="F70">
-        <v>104.788</v>
+        <v>106.329</v>
       </c>
       <c r="G70">
         <v>96</v>
@@ -7149,37 +7149,37 @@
         <v>11.1</v>
       </c>
       <c r="M70">
-        <v>21.0414304</v>
+        <v>21.3508632</v>
       </c>
       <c r="N70">
-        <v>-9.9414304</v>
+        <v>-10.2508632</v>
       </c>
       <c r="O70">
-        <v>-2.98242912</v>
+        <v>-3.075258960000001</v>
       </c>
       <c r="P70">
-        <v>-6.95900128</v>
+        <v>-7.175604240000002</v>
       </c>
       <c r="Q70">
-        <v>5.340998719999999</v>
+        <v>5.124395759999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3319665640330678</v>
+        <v>0.3411977435180055</v>
       </c>
       <c r="T70">
-        <v>1.995279928838264</v>
+        <v>2.059643797510466</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1582592027583828</v>
+        <v>0.1559655911242033</v>
       </c>
       <c r="W70">
-        <v>0.1690215520861167</v>
+        <v>0.16948210930226</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5275306758612761</v>
+        <v>0.5198853037473444</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2227139559091411</v>
+        <v>0.2242639559091411</v>
       </c>
       <c r="C71">
-        <v>23.37110519468888</v>
+        <v>21.53741212517988</v>
       </c>
       <c r="D71">
-        <v>33.7001051946889</v>
+        <v>33.4074121251799</v>
       </c>
       <c r="E71">
-        <v>106.329</v>
+        <v>107.87</v>
       </c>
       <c r="F71">
-        <v>106.329</v>
+        <v>107.87</v>
       </c>
       <c r="G71">
         <v>96</v>
@@ -7231,37 +7231,37 @@
         <v>11.1</v>
       </c>
       <c r="M71">
-        <v>21.3508632</v>
+        <v>21.660296</v>
       </c>
       <c r="N71">
-        <v>-10.2508632</v>
+        <v>-10.560296</v>
       </c>
       <c r="O71">
-        <v>-3.075258960000001</v>
+        <v>-3.168088800000001</v>
       </c>
       <c r="P71">
-        <v>-7.175604240000002</v>
+        <v>-7.392207200000001</v>
       </c>
       <c r="Q71">
-        <v>5.124395759999997</v>
+        <v>4.907792799999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3411977435180055</v>
+        <v>0.3510443349686057</v>
       </c>
       <c r="T71">
-        <v>2.059643797510466</v>
+        <v>2.128298590760815</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1559655911242033</v>
+        <v>0.1537375112510004</v>
       </c>
       <c r="W71">
-        <v>0.16948210930226</v>
+        <v>0.1699295077407991</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5198853037473444</v>
+        <v>0.5124583708366681</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2242639559091411</v>
+        <v>0.2258139559091411</v>
       </c>
       <c r="C72">
-        <v>21.53741212517988</v>
+        <v>19.70875948995774</v>
       </c>
       <c r="D72">
-        <v>33.4074121251799</v>
+        <v>33.11975948995774</v>
       </c>
       <c r="E72">
-        <v>107.87</v>
+        <v>109.411</v>
       </c>
       <c r="F72">
-        <v>107.87</v>
+        <v>109.411</v>
       </c>
       <c r="G72">
         <v>96</v>
@@ -7313,37 +7313,37 @@
         <v>11.1</v>
       </c>
       <c r="M72">
-        <v>21.660296</v>
+        <v>21.9697288</v>
       </c>
       <c r="N72">
-        <v>-10.560296</v>
+        <v>-10.8697288</v>
       </c>
       <c r="O72">
-        <v>-3.168088800000001</v>
+        <v>-3.260918640000001</v>
       </c>
       <c r="P72">
-        <v>-7.392207200000001</v>
+        <v>-7.608810160000002</v>
       </c>
       <c r="Q72">
-        <v>4.907792799999998</v>
+        <v>4.691189839999997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3510443349686057</v>
+        <v>0.3615700016916611</v>
       </c>
       <c r="T72">
-        <v>2.128298590760815</v>
+        <v>2.201688197338774</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1537375112510004</v>
+        <v>0.1515721941911272</v>
       </c>
       <c r="W72">
-        <v>0.1699295077407991</v>
+        <v>0.1703643034064217</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5124583708366681</v>
+        <v>0.5052406473037573</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2258139559091411</v>
+        <v>0.2542031083613004</v>
       </c>
       <c r="C73">
-        <v>19.70875948995776</v>
+        <v>13.65610940598107</v>
       </c>
       <c r="D73">
-        <v>33.11975948995774</v>
+        <v>28.60810940598107</v>
       </c>
       <c r="E73">
-        <v>109.411</v>
+        <v>110.952</v>
       </c>
       <c r="F73">
-        <v>109.411</v>
+        <v>110.952</v>
       </c>
       <c r="G73">
         <v>96</v>
@@ -7395,45 +7395,45 @@
         <v>11.1</v>
       </c>
       <c r="M73">
-        <v>21.9697288</v>
+        <v>26.1624816</v>
       </c>
       <c r="N73">
-        <v>-10.8697288</v>
+        <v>-15.0624816</v>
       </c>
       <c r="O73">
-        <v>-3.260918639999999</v>
+        <v>-4.51874448</v>
       </c>
       <c r="P73">
-        <v>-7.608810159999999</v>
+        <v>-10.54373712</v>
       </c>
       <c r="Q73">
-        <v>4.69118984</v>
+        <v>1.75626288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.361570001691661</v>
+        <v>0.3787016176526464</v>
       </c>
       <c r="T73">
-        <v>2.201688197338773</v>
+        <v>2.321137405498429</v>
       </c>
       <c r="U73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1515721941911272</v>
+        <v>0.127281503754598</v>
       </c>
       <c r="W73">
-        <v>0.1703643034064217</v>
+        <v>0.2057870214146658</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5052406473037574</v>
+        <v>0.4242716791819932</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2542031083613004</v>
+        <v>0.2561031083613003</v>
       </c>
       <c r="C74">
-        <v>13.65610940598107</v>
+        <v>11.85664718782888</v>
       </c>
       <c r="D74">
-        <v>28.60810940598107</v>
+        <v>28.34964718782887</v>
       </c>
       <c r="E74">
-        <v>110.952</v>
+        <v>112.493</v>
       </c>
       <c r="F74">
-        <v>110.952</v>
+        <v>112.493</v>
       </c>
       <c r="G74">
         <v>96</v>
@@ -7477,37 +7477,37 @@
         <v>11.1</v>
       </c>
       <c r="M74">
-        <v>26.1624816</v>
+        <v>26.5258494</v>
       </c>
       <c r="N74">
-        <v>-15.0624816</v>
+        <v>-15.4258494</v>
       </c>
       <c r="O74">
-        <v>-4.51874448</v>
+        <v>-4.62775482</v>
       </c>
       <c r="P74">
-        <v>-10.54373712</v>
+        <v>-10.79809458</v>
       </c>
       <c r="Q74">
-        <v>1.75626288</v>
+        <v>1.50190542</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3787016176526464</v>
+        <v>0.391031307195337</v>
       </c>
       <c r="T74">
-        <v>2.321137405498429</v>
+        <v>2.407105457553926</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.127281503754598</v>
+        <v>0.1255379215113843</v>
       </c>
       <c r="W74">
-        <v>0.2057870214146658</v>
+        <v>0.2061981581076156</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4242716791819932</v>
+        <v>0.4184597383712809</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2561031083613003</v>
+        <v>0.2580031083613004</v>
       </c>
       <c r="C75">
-        <v>11.85664718782888</v>
+        <v>10.06181334876388</v>
       </c>
       <c r="D75">
-        <v>28.34964718782887</v>
+        <v>28.09581334876387</v>
       </c>
       <c r="E75">
-        <v>112.493</v>
+        <v>114.034</v>
       </c>
       <c r="F75">
-        <v>112.493</v>
+        <v>114.034</v>
       </c>
       <c r="G75">
         <v>96</v>
@@ -7559,37 +7559,37 @@
         <v>11.1</v>
       </c>
       <c r="M75">
-        <v>26.5258494</v>
+        <v>26.8892172</v>
       </c>
       <c r="N75">
-        <v>-15.4258494</v>
+        <v>-15.7892172</v>
       </c>
       <c r="O75">
-        <v>-4.62775482</v>
+        <v>-4.73676516</v>
       </c>
       <c r="P75">
-        <v>-10.79809458</v>
+        <v>-11.05245204</v>
       </c>
       <c r="Q75">
-        <v>1.50190542</v>
+        <v>1.247547959999997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.391031307195337</v>
+        <v>0.4043094343951577</v>
       </c>
       <c r="T75">
-        <v>2.407105457553926</v>
+        <v>2.499686436690616</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1255379215113843</v>
+        <v>0.1238414631125818</v>
       </c>
       <c r="W75">
-        <v>0.2061981581076156</v>
+        <v>0.2065981829980532</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4184597383712809</v>
+        <v>0.4128048770419392</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2580031083613004</v>
+        <v>0.2599031083613004</v>
       </c>
       <c r="C76">
-        <v>10.06181334876388</v>
+        <v>8.271484668899191</v>
       </c>
       <c r="D76">
-        <v>28.09581334876387</v>
+        <v>27.84648466889918</v>
       </c>
       <c r="E76">
-        <v>114.034</v>
+        <v>115.575</v>
       </c>
       <c r="F76">
-        <v>114.034</v>
+        <v>115.575</v>
       </c>
       <c r="G76">
         <v>96</v>
@@ -7641,37 +7641,37 @@
         <v>11.1</v>
       </c>
       <c r="M76">
-        <v>26.8892172</v>
+        <v>27.252585</v>
       </c>
       <c r="N76">
-        <v>-15.7892172</v>
+        <v>-16.152585</v>
       </c>
       <c r="O76">
-        <v>-4.73676516</v>
+        <v>-4.8457755</v>
       </c>
       <c r="P76">
-        <v>-11.05245204</v>
+        <v>-11.3068095</v>
       </c>
       <c r="Q76">
-        <v>1.247547959999997</v>
+        <v>0.9931904999999972</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4043094343951577</v>
+        <v>0.418649811770964</v>
       </c>
       <c r="T76">
-        <v>2.499686436690616</v>
+        <v>2.599673894158241</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1238414631125818</v>
+        <v>0.122190243604414</v>
       </c>
       <c r="W76">
-        <v>0.2065981829980532</v>
+        <v>0.2069875405580792</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4128048770419392</v>
+        <v>0.4073008120147134</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2599031083613004</v>
+        <v>0.2618031083613004</v>
       </c>
       <c r="C77">
-        <v>8.271484668899191</v>
+        <v>6.485542263800028</v>
       </c>
       <c r="D77">
-        <v>27.84648466889918</v>
+        <v>27.60154226380002</v>
       </c>
       <c r="E77">
-        <v>115.575</v>
+        <v>117.116</v>
       </c>
       <c r="F77">
-        <v>115.575</v>
+        <v>117.116</v>
       </c>
       <c r="G77">
         <v>96</v>
@@ -7723,37 +7723,37 @@
         <v>11.1</v>
       </c>
       <c r="M77">
-        <v>27.252585</v>
+        <v>27.6159528</v>
       </c>
       <c r="N77">
-        <v>-16.152585</v>
+        <v>-16.5159528</v>
       </c>
       <c r="O77">
-        <v>-4.8457755</v>
+        <v>-4.95478584</v>
       </c>
       <c r="P77">
-        <v>-11.3068095</v>
+        <v>-11.56116696</v>
       </c>
       <c r="Q77">
-        <v>0.9931904999999972</v>
+        <v>0.7388330399999976</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.418649811770964</v>
+        <v>0.4341852205947542</v>
       </c>
       <c r="T77">
-        <v>2.599673894158241</v>
+        <v>2.707993639748168</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.122190243604414</v>
+        <v>0.120582477241198</v>
       </c>
       <c r="W77">
-        <v>0.2069875405580792</v>
+        <v>0.2073666518665255</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4073008120147134</v>
+        <v>0.4019415908039936</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2618031083613004</v>
+        <v>0.2637031083613004</v>
       </c>
       <c r="C78">
-        <v>6.485542263800028</v>
+        <v>4.703871395469577</v>
       </c>
       <c r="D78">
-        <v>27.60154226380002</v>
+        <v>27.36087139546957</v>
       </c>
       <c r="E78">
-        <v>117.116</v>
+        <v>118.657</v>
       </c>
       <c r="F78">
-        <v>117.116</v>
+        <v>118.657</v>
       </c>
       <c r="G78">
         <v>96</v>
@@ -7805,37 +7805,37 @@
         <v>11.1</v>
       </c>
       <c r="M78">
-        <v>27.6159528</v>
+        <v>27.9793206</v>
       </c>
       <c r="N78">
-        <v>-16.5159528</v>
+        <v>-16.8793206</v>
       </c>
       <c r="O78">
-        <v>-4.95478584</v>
+        <v>-5.06379618</v>
       </c>
       <c r="P78">
-        <v>-11.56116696</v>
+        <v>-11.81552442</v>
       </c>
       <c r="Q78">
-        <v>0.7388330399999976</v>
+        <v>0.4844755799999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4341852205947542</v>
+        <v>0.4510715345336565</v>
       </c>
       <c r="T78">
-        <v>2.707993639748168</v>
+        <v>2.825732493650262</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.120582477241198</v>
+        <v>0.1190164710432604</v>
       </c>
       <c r="W78">
-        <v>0.2073666518665255</v>
+        <v>0.2077359161279992</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4019415908039936</v>
+        <v>0.3967215701442015</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2637031083613004</v>
+        <v>0.2656031083613004</v>
       </c>
       <c r="C79">
-        <v>4.703871395469577</v>
+        <v>2.926361293137703</v>
       </c>
       <c r="D79">
-        <v>27.36087139546957</v>
+        <v>27.1243612931377</v>
       </c>
       <c r="E79">
-        <v>118.657</v>
+        <v>120.198</v>
       </c>
       <c r="F79">
-        <v>118.657</v>
+        <v>120.198</v>
       </c>
       <c r="G79">
         <v>96</v>
@@ -7887,37 +7887,37 @@
         <v>11.1</v>
       </c>
       <c r="M79">
-        <v>27.9793206</v>
+        <v>28.3426884</v>
       </c>
       <c r="N79">
-        <v>-16.8793206</v>
+        <v>-17.2426884</v>
       </c>
       <c r="O79">
-        <v>-5.06379618</v>
+        <v>-5.172806519999999</v>
       </c>
       <c r="P79">
-        <v>-11.81552442</v>
+        <v>-12.06988188</v>
       </c>
       <c r="Q79">
-        <v>0.4844755799999998</v>
+        <v>0.2301181199999984</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4510715345336565</v>
+        <v>0.46949296792155</v>
       </c>
       <c r="T79">
-        <v>2.825732493650262</v>
+        <v>2.954174879725274</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1190164710432604</v>
+        <v>0.1174906188503981</v>
       </c>
       <c r="W79">
-        <v>0.2077359161279992</v>
+        <v>0.2080957120750761</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3967215701442015</v>
+        <v>0.3916353961679938</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2656031083613004</v>
+        <v>0.2675031083613004</v>
       </c>
       <c r="C80">
-        <v>2.926361293137703</v>
+        <v>1.152904983265074</v>
       </c>
       <c r="D80">
-        <v>27.1243612931377</v>
+        <v>26.89190498326507</v>
       </c>
       <c r="E80">
-        <v>120.198</v>
+        <v>121.739</v>
       </c>
       <c r="F80">
-        <v>120.198</v>
+        <v>121.739</v>
       </c>
       <c r="G80">
         <v>96</v>
@@ -7969,37 +7969,37 @@
         <v>11.1</v>
       </c>
       <c r="M80">
-        <v>28.3426884</v>
+        <v>28.7060562</v>
       </c>
       <c r="N80">
-        <v>-17.2426884</v>
+        <v>-17.6060562</v>
       </c>
       <c r="O80">
-        <v>-5.172806519999999</v>
+        <v>-5.281816860000001</v>
       </c>
       <c r="P80">
-        <v>-12.06988188</v>
+        <v>-12.32423934</v>
       </c>
       <c r="Q80">
-        <v>0.2301181199999984</v>
+        <v>-0.02423934000000472</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.46949296792155</v>
+        <v>0.489668823536862</v>
       </c>
       <c r="T80">
-        <v>2.954174879725274</v>
+        <v>3.094849873997906</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1174906188503981</v>
+        <v>0.1160033958269753</v>
       </c>
       <c r="W80">
-        <v>0.2080957120750761</v>
+        <v>0.2084463992639992</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3916353961679938</v>
+        <v>0.3866779860899178</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2675031083613004</v>
+        <v>0.2694031083613004</v>
       </c>
       <c r="C81">
-        <v>1.152904983265074</v>
+        <v>-0.6166008717861331</v>
       </c>
       <c r="D81">
-        <v>26.89190498326507</v>
+        <v>26.66339912821387</v>
       </c>
       <c r="E81">
-        <v>121.739</v>
+        <v>123.28</v>
       </c>
       <c r="F81">
-        <v>121.739</v>
+        <v>123.28</v>
       </c>
       <c r="G81">
         <v>96</v>
@@ -8051,37 +8051,37 @@
         <v>11.1</v>
       </c>
       <c r="M81">
-        <v>28.7060562</v>
+        <v>29.069424</v>
       </c>
       <c r="N81">
-        <v>-17.6060562</v>
+        <v>-17.969424</v>
       </c>
       <c r="O81">
-        <v>-5.281816860000001</v>
+        <v>-5.390827200000001</v>
       </c>
       <c r="P81">
-        <v>-12.32423934</v>
+        <v>-12.5785968</v>
       </c>
       <c r="Q81">
-        <v>-0.02423934000000472</v>
+        <v>-0.2785968000000043</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.489668823536862</v>
+        <v>0.5118622647137051</v>
       </c>
       <c r="T81">
-        <v>3.094849873997906</v>
+        <v>3.249592367697802</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1160033958269753</v>
+        <v>0.1145533533791381</v>
       </c>
       <c r="W81">
-        <v>0.2084463992639992</v>
+        <v>0.2087883192731992</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3866779860899178</v>
+        <v>0.3818445112637938</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2694031083613004</v>
+        <v>0.2713031083613004</v>
       </c>
       <c r="C82">
-        <v>-0.6166008717861331</v>
+        <v>-2.382256126925398</v>
       </c>
       <c r="D82">
-        <v>26.66339912821387</v>
+        <v>26.43874387307461</v>
       </c>
       <c r="E82">
-        <v>123.28</v>
+        <v>124.821</v>
       </c>
       <c r="F82">
-        <v>123.28</v>
+        <v>124.821</v>
       </c>
       <c r="G82">
         <v>96</v>
@@ -8133,37 +8133,37 @@
         <v>11.1</v>
       </c>
       <c r="M82">
-        <v>29.069424</v>
+        <v>29.4327918</v>
       </c>
       <c r="N82">
-        <v>-17.969424</v>
+        <v>-18.3327918</v>
       </c>
       <c r="O82">
-        <v>-5.390827200000001</v>
+        <v>-5.499837540000001</v>
       </c>
       <c r="P82">
-        <v>-12.5785968</v>
+        <v>-12.83295426</v>
       </c>
       <c r="Q82">
-        <v>-0.2785968000000043</v>
+        <v>-0.5329542600000021</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5118622647137051</v>
+        <v>0.5363918575933738</v>
       </c>
       <c r="T82">
-        <v>3.249592367697802</v>
+        <v>3.420623544945055</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1145533533791381</v>
+        <v>0.1131391144485315</v>
       </c>
       <c r="W82">
-        <v>0.2087883192731992</v>
+        <v>0.2091217968130363</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3818445112637938</v>
+        <v>0.377130381495105</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2713031083613004</v>
+        <v>0.2732031083613004</v>
       </c>
       <c r="C83">
-        <v>-2.382256126925398</v>
+        <v>-4.144157299828592</v>
       </c>
       <c r="D83">
-        <v>26.43874387307461</v>
+        <v>26.21784270017142</v>
       </c>
       <c r="E83">
-        <v>124.821</v>
+        <v>126.362</v>
       </c>
       <c r="F83">
-        <v>124.821</v>
+        <v>126.362</v>
       </c>
       <c r="G83">
         <v>96</v>
@@ -8215,37 +8215,37 @@
         <v>11.1</v>
       </c>
       <c r="M83">
-        <v>29.4327918</v>
+        <v>29.7961596</v>
       </c>
       <c r="N83">
-        <v>-18.3327918</v>
+        <v>-18.6961596</v>
       </c>
       <c r="O83">
-        <v>-5.499837540000001</v>
+        <v>-5.60884788</v>
       </c>
       <c r="P83">
-        <v>-12.83295426</v>
+        <v>-13.08731172</v>
       </c>
       <c r="Q83">
-        <v>-0.5329542600000021</v>
+        <v>-0.7873117200000035</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5363918575933738</v>
+        <v>0.5636469607930056</v>
       </c>
       <c r="T83">
-        <v>3.420623544945055</v>
+        <v>3.610658186330891</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1131391144485315</v>
+        <v>0.1117593691503787</v>
       </c>
       <c r="W83">
-        <v>0.2091217968130363</v>
+        <v>0.2094471407543407</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.377130381495105</v>
+        <v>0.3725312305012624</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2732031083613004</v>
+        <v>0.2751031083613004</v>
       </c>
       <c r="C84">
-        <v>-4.144157299828592</v>
+        <v>-5.902397709199036</v>
       </c>
       <c r="D84">
-        <v>26.21784270017142</v>
+        <v>26.00060229080097</v>
       </c>
       <c r="E84">
-        <v>126.362</v>
+        <v>127.903</v>
       </c>
       <c r="F84">
-        <v>126.362</v>
+        <v>127.903</v>
       </c>
       <c r="G84">
         <v>96</v>
@@ -8297,37 +8297,37 @@
         <v>11.1</v>
       </c>
       <c r="M84">
-        <v>29.7961596</v>
+        <v>30.1595274</v>
       </c>
       <c r="N84">
-        <v>-18.6961596</v>
+        <v>-19.0595274</v>
       </c>
       <c r="O84">
-        <v>-5.60884788</v>
+        <v>-5.71785822</v>
       </c>
       <c r="P84">
-        <v>-13.08731172</v>
+        <v>-13.34166918</v>
       </c>
       <c r="Q84">
-        <v>-0.7873117200000035</v>
+        <v>-1.041669180000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5636469607930056</v>
+        <v>0.5941085467220061</v>
       </c>
       <c r="T84">
-        <v>3.610658186330891</v>
+        <v>3.823049844350356</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1117593691503787</v>
+        <v>0.1104128707268801</v>
       </c>
       <c r="W84">
-        <v>0.2094471407543407</v>
+        <v>0.2097646450826017</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3725312305012624</v>
+        <v>0.3680429024229339</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2751031083613004</v>
+        <v>0.2770031083613004</v>
       </c>
       <c r="C85">
-        <v>-5.902397709199036</v>
+        <v>-7.657067606211513</v>
       </c>
       <c r="D85">
-        <v>26.00060229080097</v>
+        <v>25.7869323937885</v>
       </c>
       <c r="E85">
-        <v>127.903</v>
+        <v>129.444</v>
       </c>
       <c r="F85">
-        <v>127.903</v>
+        <v>129.444</v>
       </c>
       <c r="G85">
         <v>96</v>
@@ -8379,37 +8379,37 @@
         <v>11.1</v>
       </c>
       <c r="M85">
-        <v>30.1595274</v>
+        <v>30.5228952</v>
       </c>
       <c r="N85">
-        <v>-19.0595274</v>
+        <v>-19.42289520000001</v>
       </c>
       <c r="O85">
-        <v>-5.71785822</v>
+        <v>-5.826868560000002</v>
       </c>
       <c r="P85">
-        <v>-13.34166918</v>
+        <v>-13.59602664000001</v>
       </c>
       <c r="Q85">
-        <v>-1.041669180000001</v>
+        <v>-1.296026640000006</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5941085467220061</v>
+        <v>0.6283778308921315</v>
       </c>
       <c r="T85">
-        <v>3.823049844350356</v>
+        <v>4.061990459622254</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1104128707268801</v>
+        <v>0.1090984317896554</v>
       </c>
       <c r="W85">
-        <v>0.2097646450826017</v>
+        <v>0.2100745897839993</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3680429024229339</v>
+        <v>0.3636614392988512</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2770031083613004</v>
+        <v>0.2789031083613004</v>
       </c>
       <c r="C86">
-        <v>-7.657067606211484</v>
+        <v>-9.408254299527727</v>
       </c>
       <c r="D86">
-        <v>25.7869323937885</v>
+        <v>25.57674570047227</v>
       </c>
       <c r="E86">
-        <v>129.444</v>
+        <v>130.985</v>
       </c>
       <c r="F86">
-        <v>129.444</v>
+        <v>130.985</v>
       </c>
       <c r="G86">
         <v>96</v>
@@ -8461,37 +8461,37 @@
         <v>11.1</v>
       </c>
       <c r="M86">
-        <v>30.5228952</v>
+        <v>30.886263</v>
       </c>
       <c r="N86">
-        <v>-19.4228952</v>
+        <v>-19.786263</v>
       </c>
       <c r="O86">
-        <v>-5.826868559999999</v>
+        <v>-5.9358789</v>
       </c>
       <c r="P86">
-        <v>-13.59602664</v>
+        <v>-13.8503841</v>
       </c>
       <c r="Q86">
-        <v>-1.296026640000001</v>
+        <v>-1.5503841</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6283778308921312</v>
+        <v>0.6672163529516065</v>
       </c>
       <c r="T86">
-        <v>4.061990459622251</v>
+        <v>4.332789823597068</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1090984317896554</v>
+        <v>0.1078149208274242</v>
       </c>
       <c r="W86">
-        <v>0.2100745897839993</v>
+        <v>0.2103772416688934</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3636614392988513</v>
+        <v>0.3593830694247472</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2789031083613004</v>
+        <v>0.2808031083613004</v>
       </c>
       <c r="C87">
-        <v>-9.408254299527727</v>
+        <v>-11.15604227424755</v>
       </c>
       <c r="D87">
-        <v>25.57674570047227</v>
+        <v>25.36995772575243</v>
       </c>
       <c r="E87">
-        <v>130.985</v>
+        <v>132.526</v>
       </c>
       <c r="F87">
-        <v>130.985</v>
+        <v>132.526</v>
       </c>
       <c r="G87">
         <v>96</v>
@@ -8543,37 +8543,37 @@
         <v>11.1</v>
       </c>
       <c r="M87">
-        <v>30.886263</v>
+        <v>31.2496308</v>
       </c>
       <c r="N87">
-        <v>-19.786263</v>
+        <v>-20.1496308</v>
       </c>
       <c r="O87">
-        <v>-5.9358789</v>
+        <v>-6.044889239999999</v>
       </c>
       <c r="P87">
-        <v>-13.8503841</v>
+        <v>-14.10474156</v>
       </c>
       <c r="Q87">
-        <v>-1.5503841</v>
+        <v>-1.804741559999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6672163529516065</v>
+        <v>0.7116032353052928</v>
       </c>
       <c r="T87">
-        <v>4.332789823597068</v>
+        <v>4.642274810996859</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1078149208274242</v>
+        <v>0.1065612589573378</v>
       </c>
       <c r="W87">
-        <v>0.2103772416688934</v>
+        <v>0.2106728551378597</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3593830694247472</v>
+        <v>0.3552041965244594</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2808031083613004</v>
+        <v>0.2827031083613004</v>
       </c>
       <c r="C88">
-        <v>-11.15604227424755</v>
+        <v>-12.90051330513593</v>
       </c>
       <c r="D88">
-        <v>25.36995772575243</v>
+        <v>25.16648669486408</v>
       </c>
       <c r="E88">
-        <v>132.526</v>
+        <v>134.067</v>
       </c>
       <c r="F88">
-        <v>132.526</v>
+        <v>134.067</v>
       </c>
       <c r="G88">
         <v>96</v>
@@ -8625,37 +8625,37 @@
         <v>11.1</v>
       </c>
       <c r="M88">
-        <v>31.2496308</v>
+        <v>31.6129986</v>
       </c>
       <c r="N88">
-        <v>-20.1496308</v>
+        <v>-20.5129986</v>
       </c>
       <c r="O88">
-        <v>-6.044889239999999</v>
+        <v>-6.153899580000001</v>
       </c>
       <c r="P88">
-        <v>-14.10474156</v>
+        <v>-14.35909902</v>
       </c>
       <c r="Q88">
-        <v>-1.804741559999998</v>
+        <v>-2.059099020000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7116032353052928</v>
+        <v>0.7628188687903152</v>
       </c>
       <c r="T88">
-        <v>4.642274810996859</v>
+        <v>4.999372873381232</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1065612589573378</v>
+        <v>0.1053364169003569</v>
       </c>
       <c r="W88">
-        <v>0.2106728551378597</v>
+        <v>0.2109616728948958</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3552041965244594</v>
+        <v>0.3511213896678564</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2827031083613004</v>
+        <v>0.2846031083613004</v>
       </c>
       <c r="C89">
-        <v>-12.90051330513593</v>
+        <v>-14.64174656444467</v>
       </c>
       <c r="D89">
-        <v>25.16648669486408</v>
+        <v>24.96625343555534</v>
       </c>
       <c r="E89">
-        <v>134.067</v>
+        <v>135.608</v>
       </c>
       <c r="F89">
-        <v>134.067</v>
+        <v>135.608</v>
       </c>
       <c r="G89">
         <v>96</v>
@@ -8707,37 +8707,37 @@
         <v>11.1</v>
       </c>
       <c r="M89">
-        <v>31.6129986</v>
+        <v>31.9763664</v>
       </c>
       <c r="N89">
-        <v>-20.5129986</v>
+        <v>-20.8763664</v>
       </c>
       <c r="O89">
-        <v>-6.153899580000001</v>
+        <v>-6.26290992</v>
       </c>
       <c r="P89">
-        <v>-14.35909902</v>
+        <v>-14.61345648</v>
       </c>
       <c r="Q89">
-        <v>-2.059099020000003</v>
+        <v>-2.313456480000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7628188687903152</v>
+        <v>0.8225704411895085</v>
       </c>
       <c r="T89">
-        <v>4.999372873381232</v>
+        <v>5.415987279496337</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1053364169003569</v>
+        <v>0.1041394121628529</v>
       </c>
       <c r="W89">
-        <v>0.2109616728948958</v>
+        <v>0.2112439266119993</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3511213896678564</v>
+        <v>0.3471313738761762</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2846031083613004</v>
+        <v>0.2865031083613004</v>
       </c>
       <c r="C90">
-        <v>-14.64174656444467</v>
+        <v>-16.3798187246278</v>
       </c>
       <c r="D90">
-        <v>24.96625343555534</v>
+        <v>24.76918127537221</v>
       </c>
       <c r="E90">
-        <v>135.608</v>
+        <v>137.149</v>
       </c>
       <c r="F90">
-        <v>135.608</v>
+        <v>137.149</v>
       </c>
       <c r="G90">
         <v>96</v>
@@ -8789,37 +8789,37 @@
         <v>11.1</v>
       </c>
       <c r="M90">
-        <v>31.9763664</v>
+        <v>32.3397342</v>
       </c>
       <c r="N90">
-        <v>-20.8763664</v>
+        <v>-21.2397342</v>
       </c>
       <c r="O90">
-        <v>-6.26290992</v>
+        <v>-6.37192026</v>
       </c>
       <c r="P90">
-        <v>-14.61345648</v>
+        <v>-14.86781394</v>
       </c>
       <c r="Q90">
-        <v>-2.313456480000003</v>
+        <v>-2.567813940000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8225704411895085</v>
+        <v>0.8931859358431</v>
       </c>
       <c r="T90">
-        <v>5.415987279496337</v>
+        <v>5.908349759450548</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1041394121628529</v>
+        <v>0.1029693064082141</v>
       </c>
       <c r="W90">
-        <v>0.2112439266119993</v>
+        <v>0.2115198375489432</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3471313738761762</v>
+        <v>0.3432310213607136</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2865031083613004</v>
+        <v>0.2884031083613003</v>
       </c>
       <c r="C91">
-        <v>-16.3798187246278</v>
+        <v>-18.11480405623004</v>
       </c>
       <c r="D91">
-        <v>24.76918127537221</v>
+        <v>24.57519594376995</v>
       </c>
       <c r="E91">
-        <v>137.149</v>
+        <v>138.69</v>
       </c>
       <c r="F91">
-        <v>137.149</v>
+        <v>138.69</v>
       </c>
       <c r="G91">
         <v>96</v>
@@ -8871,37 +8871,37 @@
         <v>11.1</v>
       </c>
       <c r="M91">
-        <v>32.3397342</v>
+        <v>32.703102</v>
       </c>
       <c r="N91">
-        <v>-21.2397342</v>
+        <v>-21.603102</v>
       </c>
       <c r="O91">
-        <v>-6.37192026</v>
+        <v>-6.4809306</v>
       </c>
       <c r="P91">
-        <v>-14.86781394</v>
+        <v>-15.1221714</v>
       </c>
       <c r="Q91">
-        <v>-2.567813940000002</v>
+        <v>-2.8221714</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8931859358431</v>
+        <v>0.9779245294274103</v>
       </c>
       <c r="T91">
-        <v>5.908349759450548</v>
+        <v>6.499184735395604</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1029693064082141</v>
+        <v>0.1018252030036784</v>
       </c>
       <c r="W91">
-        <v>0.2115198375489432</v>
+        <v>0.2117896171317326</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3432310213607136</v>
+        <v>0.3394173433455946</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2884031083613003</v>
+        <v>0.2903031083613004</v>
       </c>
       <c r="C92">
-        <v>-18.11480405623004</v>
+        <v>-19.84677452121147</v>
       </c>
       <c r="D92">
-        <v>24.57519594376995</v>
+        <v>24.38422547878852</v>
       </c>
       <c r="E92">
-        <v>138.69</v>
+        <v>140.231</v>
       </c>
       <c r="F92">
-        <v>138.69</v>
+        <v>140.231</v>
       </c>
       <c r="G92">
         <v>96</v>
@@ -8953,37 +8953,37 @@
         <v>11.1</v>
       </c>
       <c r="M92">
-        <v>32.703102</v>
+        <v>33.0664698</v>
       </c>
       <c r="N92">
-        <v>-21.603102</v>
+        <v>-21.9664698</v>
       </c>
       <c r="O92">
-        <v>-6.4809306</v>
+        <v>-6.589940939999999</v>
       </c>
       <c r="P92">
-        <v>-15.1221714</v>
+        <v>-15.37652886</v>
       </c>
       <c r="Q92">
-        <v>-2.8221714</v>
+        <v>-3.076528860000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9779245294274103</v>
+        <v>1.081493921586011</v>
       </c>
       <c r="T92">
-        <v>6.499184735395604</v>
+        <v>7.221316372661782</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1018252030036784</v>
+        <v>0.1007062447289127</v>
       </c>
       <c r="W92">
-        <v>0.2117896171317326</v>
+        <v>0.2120534674929224</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3394173433455946</v>
+        <v>0.3356874824297089</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2903031083613004</v>
+        <v>0.2922031083613004</v>
       </c>
       <c r="C93">
-        <v>-19.84677452121147</v>
+        <v>-21.57579986195421</v>
       </c>
       <c r="D93">
-        <v>24.38422547878852</v>
+        <v>24.19620013804579</v>
       </c>
       <c r="E93">
-        <v>140.231</v>
+        <v>141.772</v>
       </c>
       <c r="F93">
-        <v>140.231</v>
+        <v>141.772</v>
       </c>
       <c r="G93">
         <v>96</v>
@@ -9035,37 +9035,37 @@
         <v>11.1</v>
       </c>
       <c r="M93">
-        <v>33.0664698</v>
+        <v>33.4298376</v>
       </c>
       <c r="N93">
-        <v>-21.9664698</v>
+        <v>-22.3298376</v>
       </c>
       <c r="O93">
-        <v>-6.589940939999999</v>
+        <v>-6.698951279999999</v>
       </c>
       <c r="P93">
-        <v>-15.37652886</v>
+        <v>-15.63088632</v>
       </c>
       <c r="Q93">
-        <v>-3.076528860000002</v>
+        <v>-3.330886319999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.081493921586011</v>
+        <v>1.210955661784263</v>
       </c>
       <c r="T93">
-        <v>7.221316372661782</v>
+        <v>8.123980919244508</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1007062447289127</v>
+        <v>0.09961161163403318</v>
       </c>
       <c r="W93">
-        <v>0.2120534674929224</v>
+        <v>0.212311581976695</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3356874824297089</v>
+        <v>0.3320387054467774</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2922031083613004</v>
+        <v>0.2941031083613004</v>
       </c>
       <c r="C94">
-        <v>-21.57579986195421</v>
+        <v>-23.30194768618277</v>
       </c>
       <c r="D94">
-        <v>24.19620013804579</v>
+        <v>24.01105231381721</v>
       </c>
       <c r="E94">
-        <v>141.772</v>
+        <v>143.313</v>
       </c>
       <c r="F94">
-        <v>141.772</v>
+        <v>143.313</v>
       </c>
       <c r="G94">
         <v>96</v>
@@ -9117,37 +9117,37 @@
         <v>11.1</v>
       </c>
       <c r="M94">
-        <v>33.4298376</v>
+        <v>33.7932054</v>
       </c>
       <c r="N94">
-        <v>-22.3298376</v>
+        <v>-22.6932054</v>
       </c>
       <c r="O94">
-        <v>-6.698951279999999</v>
+        <v>-6.807961619999999</v>
       </c>
       <c r="P94">
-        <v>-15.63088632</v>
+        <v>-15.88524378</v>
       </c>
       <c r="Q94">
-        <v>-3.330886319999999</v>
+        <v>-3.585243779999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.210955661784263</v>
+        <v>1.377406470610587</v>
       </c>
       <c r="T94">
-        <v>8.123980919244508</v>
+        <v>9.284549621993724</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09961161163403318</v>
+        <v>0.09854051903581777</v>
       </c>
       <c r="W94">
-        <v>0.212311581976695</v>
+        <v>0.2125641456113542</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3320387054467774</v>
+        <v>0.3284683967860593</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2941031083613004</v>
+        <v>0.2960031083613004</v>
       </c>
       <c r="C95">
-        <v>-23.30194768618277</v>
+        <v>-25.02528354801539</v>
       </c>
       <c r="D95">
-        <v>24.01105231381721</v>
+        <v>23.82871645198462</v>
       </c>
       <c r="E95">
-        <v>143.313</v>
+        <v>144.854</v>
       </c>
       <c r="F95">
-        <v>143.313</v>
+        <v>144.854</v>
       </c>
       <c r="G95">
         <v>96</v>
@@ -9199,37 +9199,37 @@
         <v>11.1</v>
       </c>
       <c r="M95">
-        <v>33.7932054</v>
+        <v>34.1565732</v>
       </c>
       <c r="N95">
-        <v>-22.6932054</v>
+        <v>-23.0565732</v>
       </c>
       <c r="O95">
-        <v>-6.807961619999999</v>
+        <v>-6.916971960000001</v>
       </c>
       <c r="P95">
-        <v>-15.88524378</v>
+        <v>-16.13960124</v>
       </c>
       <c r="Q95">
-        <v>-3.585243779999999</v>
+        <v>-3.839601240000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.377406470610587</v>
+        <v>1.599340882379018</v>
       </c>
       <c r="T95">
-        <v>9.284549621993724</v>
+        <v>10.83197455899268</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09854051903581777</v>
+        <v>0.0974922156418197</v>
       </c>
       <c r="W95">
-        <v>0.2125641456113542</v>
+        <v>0.2128113355516589</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3284683967860593</v>
+        <v>0.324974052139399</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2960031083613004</v>
+        <v>0.2979031083613004</v>
       </c>
       <c r="C96">
-        <v>-25.02528354801539</v>
+        <v>-26.7458710253498</v>
       </c>
       <c r="D96">
-        <v>23.82871645198462</v>
+        <v>23.6491289746502</v>
       </c>
       <c r="E96">
-        <v>144.854</v>
+        <v>146.395</v>
       </c>
       <c r="F96">
-        <v>144.854</v>
+        <v>146.395</v>
       </c>
       <c r="G96">
         <v>96</v>
@@ -9281,37 +9281,37 @@
         <v>11.1</v>
       </c>
       <c r="M96">
-        <v>34.1565732</v>
+        <v>34.519941</v>
       </c>
       <c r="N96">
-        <v>-23.0565732</v>
+        <v>-23.419941</v>
       </c>
       <c r="O96">
-        <v>-6.916971960000001</v>
+        <v>-7.0259823</v>
       </c>
       <c r="P96">
-        <v>-16.13960124</v>
+        <v>-16.3939587</v>
       </c>
       <c r="Q96">
-        <v>-3.839601240000002</v>
+        <v>-4.093958700000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.599340882379018</v>
+        <v>1.910049058854823</v>
       </c>
       <c r="T96">
-        <v>10.83197455899268</v>
+        <v>12.99836947079122</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0974922156418197</v>
+        <v>0.09646598179295844</v>
       </c>
       <c r="W96">
-        <v>0.2128113355516589</v>
+        <v>0.2130533214932204</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.324974052139399</v>
+        <v>0.3215532726431949</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2979031083613004</v>
+        <v>0.2998031083613004</v>
       </c>
       <c r="C97">
-        <v>-26.7458710253498</v>
+        <v>-28.4637717937763</v>
       </c>
       <c r="D97">
-        <v>23.6491289746502</v>
+        <v>23.4722282062237</v>
       </c>
       <c r="E97">
-        <v>146.395</v>
+        <v>147.936</v>
       </c>
       <c r="F97">
-        <v>146.395</v>
+        <v>147.936</v>
       </c>
       <c r="G97">
         <v>96</v>
@@ -9363,37 +9363,37 @@
         <v>11.1</v>
       </c>
       <c r="M97">
-        <v>34.519941</v>
+        <v>34.8833088</v>
       </c>
       <c r="N97">
-        <v>-23.419941</v>
+        <v>-23.7833088</v>
       </c>
       <c r="O97">
-        <v>-7.0259823</v>
+        <v>-7.13499264</v>
       </c>
       <c r="P97">
-        <v>-16.3939587</v>
+        <v>-16.64831616</v>
       </c>
       <c r="Q97">
-        <v>-4.093958700000004</v>
+        <v>-4.348316160000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.910049058854823</v>
+        <v>2.376111323568529</v>
       </c>
       <c r="T97">
-        <v>12.99836947079122</v>
+        <v>16.24796183848904</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09646598179295844</v>
+        <v>0.09546112781594845</v>
       </c>
       <c r="W97">
-        <v>0.2130533214932204</v>
+        <v>0.2132902660609994</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3215532726431949</v>
+        <v>0.3182037593864949</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2998031083613004</v>
+        <v>0.3017031083613004</v>
       </c>
       <c r="C98">
-        <v>-28.46377179377627</v>
+        <v>-30.17904569719784</v>
       </c>
       <c r="D98">
-        <v>23.4722282062237</v>
+        <v>23.29795430280218</v>
       </c>
       <c r="E98">
-        <v>147.936</v>
+        <v>149.477</v>
       </c>
       <c r="F98">
-        <v>147.936</v>
+        <v>149.477</v>
       </c>
       <c r="G98">
         <v>96</v>
@@ -9445,37 +9445,37 @@
         <v>11.1</v>
       </c>
       <c r="M98">
-        <v>34.88330879999999</v>
+        <v>35.2466766</v>
       </c>
       <c r="N98">
-        <v>-23.78330879999999</v>
+        <v>-24.1466766</v>
       </c>
       <c r="O98">
-        <v>-7.134992639999997</v>
+        <v>-7.244002979999999</v>
       </c>
       <c r="P98">
-        <v>-16.64831616</v>
+        <v>-16.90267362</v>
       </c>
       <c r="Q98">
-        <v>-4.348316159999998</v>
+        <v>-4.602673620000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.376111323568523</v>
+        <v>3.152881764758031</v>
       </c>
       <c r="T98">
-        <v>16.24796183848899</v>
+        <v>21.66394911798533</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09546112781594847</v>
+        <v>0.09447699247763972</v>
       </c>
       <c r="W98">
-        <v>0.2132902660609994</v>
+        <v>0.2135223251737726</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.318203759386495</v>
+        <v>0.3149233082587991</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3017031083613004</v>
+        <v>0.3036031083613003</v>
       </c>
       <c r="C99">
-        <v>-30.17904569719784</v>
+        <v>-31.8917508153273</v>
       </c>
       <c r="D99">
-        <v>23.29795430280218</v>
+        <v>23.1262491846727</v>
       </c>
       <c r="E99">
-        <v>149.477</v>
+        <v>151.018</v>
       </c>
       <c r="F99">
-        <v>149.477</v>
+        <v>151.018</v>
       </c>
       <c r="G99">
         <v>96</v>
@@ -9527,37 +9527,37 @@
         <v>11.1</v>
       </c>
       <c r="M99">
-        <v>35.2466766</v>
+        <v>35.6100444</v>
       </c>
       <c r="N99">
-        <v>-24.1466766</v>
+        <v>-24.5100444</v>
       </c>
       <c r="O99">
-        <v>-7.244002979999999</v>
+        <v>-7.353013319999999</v>
       </c>
       <c r="P99">
-        <v>-16.90267362</v>
+        <v>-17.15703108</v>
       </c>
       <c r="Q99">
-        <v>-4.602673620000003</v>
+        <v>-4.857031080000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.152881764758031</v>
+        <v>4.706422647137045</v>
       </c>
       <c r="T99">
-        <v>21.66394911798533</v>
+        <v>32.49592367697798</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09447699247763972</v>
+        <v>0.09351294153399033</v>
       </c>
       <c r="W99">
-        <v>0.2135223251737726</v>
+        <v>0.2137496483862851</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3149233082587991</v>
+        <v>0.3117098051133012</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3036031083613003</v>
+        <v>0.3055031083613004</v>
       </c>
       <c r="C100">
-        <v>-31.8917508153273</v>
+        <v>-33.60194352822217</v>
       </c>
       <c r="D100">
-        <v>23.1262491846727</v>
+        <v>22.95705647177783</v>
       </c>
       <c r="E100">
-        <v>151.018</v>
+        <v>152.559</v>
       </c>
       <c r="F100">
-        <v>151.018</v>
+        <v>152.559</v>
       </c>
       <c r="G100">
         <v>96</v>
@@ -9609,37 +9609,37 @@
         <v>11.1</v>
       </c>
       <c r="M100">
-        <v>35.6100444</v>
+        <v>35.9734122</v>
       </c>
       <c r="N100">
-        <v>-24.5100444</v>
+        <v>-24.8734122</v>
       </c>
       <c r="O100">
-        <v>-7.353013319999999</v>
+        <v>-7.462023659999999</v>
       </c>
       <c r="P100">
-        <v>-17.15703108</v>
+        <v>-17.41138854</v>
       </c>
       <c r="Q100">
-        <v>-4.857031080000001</v>
+        <v>-5.111388539999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.706422647137045</v>
+        <v>9.367045294274092</v>
       </c>
       <c r="T100">
-        <v>32.49592367697798</v>
+        <v>64.99184735395598</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09351294153399033</v>
+        <v>0.09256836636698033</v>
       </c>
       <c r="W100">
-        <v>0.2137496483862851</v>
+        <v>0.2139723792106661</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3117098051133012</v>
+        <v>0.3085612212232678</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3055031083613004</v>
-      </c>
-      <c r="C101">
-        <v>-33.60194352822217</v>
-      </c>
-      <c r="D101">
-        <v>22.95705647177783</v>
-      </c>
-      <c r="E101">
-        <v>152.559</v>
-      </c>
-      <c r="F101">
-        <v>152.559</v>
-      </c>
-      <c r="G101">
-        <v>96</v>
-      </c>
-      <c r="H101">
-        <v>154.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.4</v>
-      </c>
-      <c r="K101">
-        <v>12.3</v>
-      </c>
-      <c r="L101">
-        <v>11.1</v>
-      </c>
-      <c r="M101">
-        <v>35.9734122</v>
-      </c>
-      <c r="N101">
-        <v>-24.8734122</v>
-      </c>
-      <c r="O101">
-        <v>-7.462023659999999</v>
-      </c>
-      <c r="P101">
-        <v>-17.41138854</v>
-      </c>
-      <c r="Q101">
-        <v>-5.111388539999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.367045294274092</v>
-      </c>
-      <c r="T101">
-        <v>64.99184735395598</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09256836636698033</v>
-      </c>
-      <c r="W101">
-        <v>0.2139723792106661</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3085612212232678</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
